--- a/src/attributions/attributions_saliency_traj_371.xlsx
+++ b/src/attributions/attributions_saliency_traj_371.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GG9"/>
+  <dimension ref="A1:GG15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1568,1709 +1568,1709 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.09465231001377106</v>
+        <v>0.001573086599819362</v>
       </c>
       <c r="B3" t="n">
-        <v>0.5895640850067139</v>
+        <v>0.0001314558321610093</v>
       </c>
       <c r="C3" t="n">
-        <v>0.4446361064910889</v>
+        <v>0.0004491892468649894</v>
       </c>
       <c r="D3" t="n">
-        <v>0.41355100274086</v>
+        <v>6.645802932325751e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5795965790748596</v>
+        <v>0.0004357626603450626</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2994103729724884</v>
+        <v>0.001056170789524913</v>
       </c>
       <c r="G3" t="n">
-        <v>0.07005201280117035</v>
+        <v>0.0003638550406321883</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1397377997636795</v>
+        <v>0.0006684086984023452</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4019360244274139</v>
+        <v>0.0005970240454189479</v>
       </c>
       <c r="J3" t="n">
-        <v>0.4331850409507751</v>
+        <v>0.001738073187880218</v>
       </c>
       <c r="K3" t="n">
-        <v>0.351203590631485</v>
+        <v>0.000669010216370225</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1777405291795731</v>
+        <v>0.0003264832485001534</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1894581317901611</v>
+        <v>0.001035002060234547</v>
       </c>
       <c r="N3" t="n">
-        <v>0.422868937253952</v>
+        <v>0.0007363708573393524</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1459148526191711</v>
+        <v>0.0009736391366459429</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2115896791219711</v>
+        <v>0.0009347946615889668</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.06909185647964478</v>
+        <v>0.0005924461875110865</v>
       </c>
       <c r="R3" t="n">
-        <v>0.56094890832901</v>
+        <v>0.0002575201797299087</v>
       </c>
       <c r="S3" t="n">
-        <v>0.003060423769056797</v>
+        <v>3.256848140154034e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1256668418645859</v>
+        <v>0.0003047016798518598</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2419672012329102</v>
+        <v>0.0003340572584420443</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1463738977909088</v>
+        <v>1.037906622514129e-05</v>
       </c>
       <c r="W3" t="n">
-        <v>0.1992208808660507</v>
+        <v>0.000158218084834516</v>
       </c>
       <c r="X3" t="n">
-        <v>0.1276547610759735</v>
+        <v>3.85992243536748e-05</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.05920004844665527</v>
+        <v>0.0001079595094779506</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.01221916452050209</v>
+        <v>0.0002708855317905545</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.1336091607809067</v>
+        <v>0.0001739495201036334</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.1638257801532745</v>
+        <v>0.0006048140930943191</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.1761161386966705</v>
+        <v>0.0002990499779116362</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.06407445669174194</v>
+        <v>4.450474807526916e-05</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.2133690863847733</v>
+        <v>0.0005878398660570383</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.03563040867447853</v>
+        <v>0.0004958994104526937</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.01902914792299271</v>
+        <v>0.0004422097699716687</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.06223407387733459</v>
+        <v>8.163043821696192e-05</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.1404264271259308</v>
+        <v>0.0003516095457598567</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.04577022790908813</v>
+        <v>2.408494765404612e-05</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.1478371620178223</v>
+        <v>1.501796214142814e-05</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.1797613203525543</v>
+        <v>0.0002814651816152036</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.1220137774944305</v>
+        <v>0.0001044605160132051</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.1411949396133423</v>
+        <v>0.0002458804519847035</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.1079305186867714</v>
+        <v>6.740216485923156e-05</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.1122176349163055</v>
+        <v>0.0001392679841956124</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.03254174441099167</v>
+        <v>0.0002952277718577534</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.0818360447883606</v>
+        <v>6.961436884012073e-05</v>
       </c>
       <c r="AS3" t="n">
-        <v>0.08622694760560989</v>
+        <v>0.0001083669558283873</v>
       </c>
       <c r="AT3" t="n">
-        <v>0.1895675659179688</v>
+        <v>0.001586091821081936</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.005902543663978577</v>
+        <v>0.0006664815009571612</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.4018878638744354</v>
+        <v>0.0005141737638041377</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.02865287102758884</v>
+        <v>0.0007765779155306518</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.7330848574638367</v>
+        <v>0.0008176473784260452</v>
       </c>
       <c r="AY3" t="n">
-        <v>0.152384489774704</v>
+        <v>0.0002537558902986348</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.03461382165551186</v>
+        <v>0.0002418413932900876</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.07114268094301224</v>
+        <v>0.0006494430708698928</v>
       </c>
       <c r="BB3" t="n">
-        <v>0.07742112129926682</v>
+        <v>0.0001425401715096086</v>
       </c>
       <c r="BC3" t="n">
-        <v>0.2653875350952148</v>
+        <v>0.0004227747558616102</v>
       </c>
       <c r="BD3" t="n">
-        <v>0.3288638889789581</v>
+        <v>0.0001747557253111154</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.1567158252000809</v>
+        <v>2.59890548477415e-05</v>
       </c>
       <c r="BF3" t="n">
-        <v>0.2155245393514633</v>
+        <v>0.0007040739292278886</v>
       </c>
       <c r="BG3" t="n">
-        <v>0.1761293113231659</v>
+        <v>0.0008368440321646631</v>
       </c>
       <c r="BH3" t="n">
-        <v>0.5424377918243408</v>
+        <v>0.0004889116971753538</v>
       </c>
       <c r="BI3" t="n">
-        <v>0.1414821892976761</v>
+        <v>0.0002652998955454677</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.2511968612670898</v>
+        <v>0.0001872280845418572</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.5113401412963867</v>
+        <v>0.0001546381827211007</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.217219278216362</v>
+        <v>0.0004193546483293176</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.09553910791873932</v>
+        <v>0.0002909137110691518</v>
       </c>
       <c r="BN3" t="n">
-        <v>0.3286504149436951</v>
+        <v>1.568442894495092e-05</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.006499270908534527</v>
+        <v>0.0006533922860398889</v>
       </c>
       <c r="BP3" t="n">
-        <v>0.1775403767824173</v>
+        <v>0.0004498982452787459</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0.01130180992186069</v>
+        <v>0.0004184059507679194</v>
       </c>
       <c r="BR3" t="n">
-        <v>0.04751444607973099</v>
+        <v>7.205086876638234e-05</v>
       </c>
       <c r="BS3" t="n">
-        <v>0.1070387959480286</v>
+        <v>0.0005478094099089503</v>
       </c>
       <c r="BT3" t="n">
-        <v>0.1226794794201851</v>
+        <v>0.0002680074248928577</v>
       </c>
       <c r="BU3" t="n">
-        <v>0.07003746181726456</v>
+        <v>0.0006470182561315596</v>
       </c>
       <c r="BV3" t="n">
-        <v>0.08581474423408508</v>
+        <v>0.0003835817915387452</v>
       </c>
       <c r="BW3" t="n">
-        <v>0.09512209892272949</v>
+        <v>0.000560661603230983</v>
       </c>
       <c r="BX3" t="n">
-        <v>0.1153947114944458</v>
+        <v>0.0001956314954441041</v>
       </c>
       <c r="BY3" t="n">
-        <v>0.5544793605804443</v>
+        <v>0.0005647436482831836</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0.01796622388064861</v>
+        <v>0.0001155673380708322</v>
       </c>
       <c r="CA3" t="n">
-        <v>0.02866697311401367</v>
+        <v>5.535111995413899e-05</v>
       </c>
       <c r="CB3" t="n">
-        <v>0.03850528225302696</v>
+        <v>0.0001710796932457015</v>
       </c>
       <c r="CC3" t="n">
-        <v>0.2562045454978943</v>
+        <v>0.0005245846696197987</v>
       </c>
       <c r="CD3" t="n">
-        <v>0.03363421931862831</v>
+        <v>0.0003075000422541052</v>
       </c>
       <c r="CE3" t="n">
-        <v>0.1225616335868835</v>
+        <v>0.0004033352597616613</v>
       </c>
       <c r="CF3" t="n">
-        <v>0.121794156730175</v>
+        <v>8.792451990302652e-05</v>
       </c>
       <c r="CG3" t="n">
-        <v>0.04636762291193008</v>
+        <v>0.0003631086729001254</v>
       </c>
       <c r="CH3" t="n">
-        <v>0.1216781809926033</v>
+        <v>0.0001230630587087944</v>
       </c>
       <c r="CI3" t="n">
-        <v>0.06400048732757568</v>
+        <v>0.0002269361866638064</v>
       </c>
       <c r="CJ3" t="n">
-        <v>0.02887418121099472</v>
+        <v>0.0001806876098271459</v>
       </c>
       <c r="CK3" t="n">
-        <v>0.1077548936009407</v>
+        <v>3.738038503797725e-05</v>
       </c>
       <c r="CL3" t="n">
-        <v>0.05409250408411026</v>
+        <v>0.0001108960932469927</v>
       </c>
       <c r="CM3" t="n">
-        <v>0.02451321296393871</v>
+        <v>0.0001619063259568065</v>
       </c>
       <c r="CN3" t="n">
-        <v>0.09548443555831909</v>
+        <v>0.0005848490400239825</v>
       </c>
       <c r="CO3" t="n">
-        <v>0.091375432908535</v>
+        <v>3.932118124794215e-05</v>
       </c>
       <c r="CP3" t="n">
-        <v>0.1648501604795456</v>
+        <v>0.000680038589052856</v>
       </c>
       <c r="CQ3" t="n">
-        <v>0.4479346871376038</v>
+        <v>0.0003823444130830467</v>
       </c>
       <c r="CR3" t="n">
-        <v>0.03349170088768005</v>
+        <v>0.0005299152689985931</v>
       </c>
       <c r="CS3" t="n">
-        <v>0.1115965619683266</v>
+        <v>0.000861329841427505</v>
       </c>
       <c r="CT3" t="n">
-        <v>0.04074453562498093</v>
+        <v>0.0005974654341116548</v>
       </c>
       <c r="CU3" t="n">
-        <v>0.05887983739376068</v>
+        <v>0.0004333065007813275</v>
       </c>
       <c r="CV3" t="n">
-        <v>0.08255595713853836</v>
+        <v>0.0002764899400062859</v>
       </c>
       <c r="CW3" t="n">
-        <v>0.1403091102838516</v>
+        <v>0.0004290353390388191</v>
       </c>
       <c r="CX3" t="n">
-        <v>0.06972121447324753</v>
+        <v>1.906400211737491e-05</v>
       </c>
       <c r="CY3" t="n">
-        <v>0.0751558393239975</v>
+        <v>0.0002763177617453039</v>
       </c>
       <c r="CZ3" t="n">
-        <v>0.005643330514431</v>
+        <v>2.502267307136208e-05</v>
       </c>
       <c r="DA3" t="n">
-        <v>0.09391439706087112</v>
+        <v>0.0002159010764444247</v>
       </c>
       <c r="DB3" t="n">
-        <v>0.02703811973333359</v>
+        <v>0.00013777005369775</v>
       </c>
       <c r="DC3" t="n">
-        <v>0.07233750820159912</v>
+        <v>2.913096250267699e-05</v>
       </c>
       <c r="DD3" t="n">
-        <v>0.05747335031628609</v>
+        <v>4.341393287177198e-05</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.07767853885889053</v>
+        <v>0.0004706112376879901</v>
       </c>
       <c r="DF3" t="n">
-        <v>0.03702561557292938</v>
+        <v>0.001134860678575933</v>
       </c>
       <c r="DG3" t="n">
-        <v>0.2253798246383667</v>
+        <v>0.0003725448914337903</v>
       </c>
       <c r="DH3" t="n">
-        <v>0.6295032501220703</v>
+        <v>0.000215959909837693</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.2564705908298492</v>
+        <v>0.0005282885394990444</v>
       </c>
       <c r="DJ3" t="n">
-        <v>0.06672008335590363</v>
+        <v>0.0006126927328296006</v>
       </c>
       <c r="DK3" t="n">
-        <v>0.2432498335838318</v>
+        <v>0.0001042893127305433</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.06769254803657532</v>
+        <v>4.56937268609181e-05</v>
       </c>
       <c r="DM3" t="n">
-        <v>0.08249648660421371</v>
+        <v>0.0006481983000412583</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.2219375371932983</v>
+        <v>0.0004599888343364</v>
       </c>
       <c r="DO3" t="n">
-        <v>0.2257036715745926</v>
+        <v>0.000286656548269093</v>
       </c>
       <c r="DP3" t="n">
-        <v>0.1464223116636276</v>
+        <v>0.0001004492660285905</v>
       </c>
       <c r="DQ3" t="n">
-        <v>0.1823973208665848</v>
+        <v>0.0002999334828928113</v>
       </c>
       <c r="DR3" t="n">
-        <v>0.2179741561412811</v>
+        <v>0.0003834894159808755</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.08177810907363892</v>
+        <v>0.0002110916975652799</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.07915285229682922</v>
+        <v>0.0001097316999221221</v>
       </c>
       <c r="DU3" t="n">
-        <v>0.05068951472640038</v>
+        <v>5.679161404259503e-06</v>
       </c>
       <c r="DV3" t="n">
-        <v>0.1208359375596046</v>
+        <v>6.196881440700963e-05</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.0530133843421936</v>
+        <v>0.0002109433262376115</v>
       </c>
       <c r="DX3" t="n">
-        <v>0.01931123435497284</v>
+        <v>6.292211764957756e-05</v>
       </c>
       <c r="DY3" t="n">
-        <v>0.1084864735603333</v>
+        <v>0.0004096756456419826</v>
       </c>
       <c r="DZ3" t="n">
-        <v>0.05120063200592995</v>
+        <v>5.49192882317584e-05</v>
       </c>
       <c r="EA3" t="n">
-        <v>0.03622050210833549</v>
+        <v>0.0001919525093398988</v>
       </c>
       <c r="EB3" t="n">
-        <v>0.1559616774320602</v>
+        <v>0.0004260533896740526</v>
       </c>
       <c r="EC3" t="n">
-        <v>0.08619816601276398</v>
+        <v>6.773884524591267e-05</v>
       </c>
       <c r="ED3" t="n">
-        <v>0.0406934916973114</v>
+        <v>9.036662959260866e-05</v>
       </c>
       <c r="EE3" t="n">
-        <v>0.04673755913972855</v>
+        <v>0.0002998091804329306</v>
       </c>
       <c r="EF3" t="n">
-        <v>0.1082504242658615</v>
+        <v>0.0001819290337152779</v>
       </c>
       <c r="EG3" t="n">
-        <v>0.03528613597154617</v>
+        <v>0.0003026050690095872</v>
       </c>
       <c r="EH3" t="n">
-        <v>0.193746879696846</v>
+        <v>1.435191188647877e-05</v>
       </c>
       <c r="EI3" t="n">
-        <v>0.09048887342214584</v>
+        <v>0.0005675405845977366</v>
       </c>
       <c r="EJ3" t="n">
-        <v>0.04832160100340843</v>
+        <v>0.0002846246352419257</v>
       </c>
       <c r="EK3" t="n">
-        <v>0.05995587259531021</v>
+        <v>0.0002854577032849193</v>
       </c>
       <c r="EL3" t="n">
-        <v>0.04749909788370132</v>
+        <v>0.0003853682137560099</v>
       </c>
       <c r="EM3" t="n">
-        <v>0.08783505856990814</v>
+        <v>0.0002248374366899952</v>
       </c>
       <c r="EN3" t="n">
-        <v>0.09608455747365952</v>
+        <v>2.031920303124934e-05</v>
       </c>
       <c r="EO3" t="n">
-        <v>0.2368815094232559</v>
+        <v>0.000348313245922327</v>
       </c>
       <c r="EP3" t="n">
-        <v>0.01655225455760956</v>
+        <v>0.0004346613131929189</v>
       </c>
       <c r="EQ3" t="n">
-        <v>0.03671763092279434</v>
+        <v>0.0002566163602750748</v>
       </c>
       <c r="ER3" t="n">
-        <v>0.177173063158989</v>
+        <v>0.0004447227111086249</v>
       </c>
       <c r="ES3" t="n">
-        <v>0.06351069360971451</v>
+        <v>0.0001525709230918437</v>
       </c>
       <c r="ET3" t="n">
-        <v>0.02397016994655132</v>
+        <v>0.0006131023401394486</v>
       </c>
       <c r="EU3" t="n">
-        <v>0.02757894434034824</v>
+        <v>0.0001710307551547885</v>
       </c>
       <c r="EV3" t="n">
-        <v>0.0607387088239193</v>
+        <v>9.748564480105415e-05</v>
       </c>
       <c r="EW3" t="n">
-        <v>0.181292936205864</v>
+        <v>0.0003694484476000071</v>
       </c>
       <c r="EX3" t="n">
-        <v>0.1062916368246078</v>
+        <v>0.000310129951685667</v>
       </c>
       <c r="EY3" t="n">
-        <v>0.08077048510313034</v>
+        <v>0.0004823544004466385</v>
       </c>
       <c r="EZ3" t="n">
-        <v>0.08996167778968811</v>
+        <v>7.414030551444739e-05</v>
       </c>
       <c r="FA3" t="n">
-        <v>0.02469983324408531</v>
+        <v>0.0001899491326184943</v>
       </c>
       <c r="FB3" t="n">
-        <v>0.03004713356494904</v>
+        <v>0.0001332019019173458</v>
       </c>
       <c r="FC3" t="n">
-        <v>0.006068406626582146</v>
+        <v>0.0002957725373562425</v>
       </c>
       <c r="FD3" t="n">
-        <v>0.0002063193824142218</v>
+        <v>0.0002414722839603201</v>
       </c>
       <c r="FE3" t="n">
-        <v>0.07770129293203354</v>
+        <v>0.0001388494711136445</v>
       </c>
       <c r="FF3" t="n">
-        <v>0.061378363519907</v>
+        <v>0.0002024802815867588</v>
       </c>
       <c r="FG3" t="n">
-        <v>0.06767378002405167</v>
+        <v>0.0009809175971895456</v>
       </c>
       <c r="FH3" t="n">
-        <v>0.05037198960781097</v>
+        <v>0.0002129336789948866</v>
       </c>
       <c r="FI3" t="n">
-        <v>0.03658942878246307</v>
+        <v>0.0002859623054973781</v>
       </c>
       <c r="FJ3" t="n">
-        <v>0.01125287637114525</v>
+        <v>0.0003294663038104773</v>
       </c>
       <c r="FK3" t="n">
-        <v>0.07779943197965622</v>
+        <v>0.0002155076945200562</v>
       </c>
       <c r="FL3" t="n">
-        <v>0.007534250617027283</v>
+        <v>0.0001592020271345973</v>
       </c>
       <c r="FM3" t="n">
-        <v>0.07966291159391403</v>
+        <v>0.0001283675082959235</v>
       </c>
       <c r="FN3" t="n">
-        <v>0.03181303292512894</v>
+        <v>6.822278373874724e-05</v>
       </c>
       <c r="FO3" t="n">
-        <v>0.07989194989204407</v>
+        <v>0.0002155752445105463</v>
       </c>
       <c r="FP3" t="n">
-        <v>0.113136850297451</v>
+        <v>0.0009185349335893989</v>
       </c>
       <c r="FQ3" t="n">
-        <v>0.3126772344112396</v>
+        <v>0.002206504810601473</v>
       </c>
       <c r="FR3" t="n">
-        <v>0.2144304513931274</v>
+        <v>0.0006807293393649161</v>
       </c>
       <c r="FS3" t="n">
-        <v>0.1063176244497299</v>
+        <v>0.0008956074016168714</v>
       </c>
       <c r="FT3" t="n">
-        <v>0.3727657794952393</v>
+        <v>0.0007578773656859994</v>
       </c>
       <c r="FU3" t="n">
-        <v>0.2471894770860672</v>
+        <v>5.151264485903084e-05</v>
       </c>
       <c r="FV3" t="n">
-        <v>0.08156441152095795</v>
+        <v>1.110511948354542e-05</v>
       </c>
       <c r="FW3" t="n">
-        <v>0.08920472115278244</v>
+        <v>0.0009324586717411876</v>
       </c>
       <c r="FX3" t="n">
-        <v>0.01746765896677971</v>
+        <v>0.0002932007773779333</v>
       </c>
       <c r="FY3" t="n">
-        <v>0.07782982289791107</v>
+        <v>0.000549378280993551</v>
       </c>
       <c r="FZ3" t="n">
-        <v>0.2546622455120087</v>
+        <v>0.0006443581078201532</v>
       </c>
       <c r="GA3" t="n">
-        <v>0.05901797488331795</v>
+        <v>0.0002806270204018801</v>
       </c>
       <c r="GB3" t="n">
-        <v>0.06159806996583939</v>
+        <v>0.0002209928497904912</v>
       </c>
       <c r="GC3" t="n">
-        <v>0.03661824762821198</v>
+        <v>0.0004530373553279787</v>
       </c>
       <c r="GD3" t="n">
-        <v>0.2204177528619766</v>
+        <v>0.0001285762700717896</v>
       </c>
       <c r="GE3" t="n">
-        <v>0.08332078903913498</v>
+        <v>0.0005204721237532794</v>
       </c>
       <c r="GF3" t="n">
-        <v>0.1075141653418541</v>
+        <v>5.102090290165506e-05</v>
       </c>
       <c r="GG3" t="n">
-        <v>0.02482767589390278</v>
+        <v>0.000134686502860859</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.009391850791871548</v>
+        <v>0.02741182222962379</v>
       </c>
       <c r="B4" t="n">
-        <v>0.1047669723629951</v>
+        <v>0.3820043504238129</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01098421588540077</v>
+        <v>0.007116422057151794</v>
       </c>
       <c r="D4" t="n">
-        <v>0.05799661204218864</v>
+        <v>0.5974743962287903</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0470319464802742</v>
+        <v>0.0376722626388073</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02062130719423294</v>
+        <v>0.08180233836174011</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01969803869724274</v>
+        <v>0.1723484247922897</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01879615522921085</v>
+        <v>0.1879931837320328</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001957504544407129</v>
+        <v>0.02538914605975151</v>
       </c>
       <c r="J4" t="n">
-        <v>0.006231416016817093</v>
+        <v>0.01612810045480728</v>
       </c>
       <c r="K4" t="n">
-        <v>0.06716711819171906</v>
+        <v>0.2979035973548889</v>
       </c>
       <c r="L4" t="n">
-        <v>0.00509859062731266</v>
+        <v>0.03026578202843666</v>
       </c>
       <c r="M4" t="n">
-        <v>0.04674411192536354</v>
+        <v>0.777039647102356</v>
       </c>
       <c r="N4" t="n">
-        <v>0.05268656462430954</v>
+        <v>0.09373891353607178</v>
       </c>
       <c r="O4" t="n">
-        <v>0.03064524568617344</v>
+        <v>0.0393250398337841</v>
       </c>
       <c r="P4" t="n">
-        <v>0.02553233876824379</v>
+        <v>0.2531721889972687</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0003487925278022885</v>
+        <v>0.05106068775057793</v>
       </c>
       <c r="R4" t="n">
-        <v>0.005903048440814018</v>
+        <v>0.03101640194654465</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0005873235641047359</v>
+        <v>0.03304097056388855</v>
       </c>
       <c r="T4" t="n">
-        <v>0.01761316694319248</v>
+        <v>0.02648833766579628</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0001263334415853024</v>
+        <v>0.03379644453525543</v>
       </c>
       <c r="V4" t="n">
-        <v>0.01538109593093395</v>
+        <v>0.01638461463153362</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0121462419629097</v>
+        <v>0.04768345132470131</v>
       </c>
       <c r="X4" t="n">
-        <v>0.0113940117880702</v>
+        <v>0.0868641659617424</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.01260539796203375</v>
+        <v>0.01712916046380997</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.01304450910538435</v>
+        <v>0.1267011016607285</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.009683120995759964</v>
+        <v>0.002828868106007576</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.0007586153224110603</v>
+        <v>0.01052282005548477</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.01278802659362555</v>
+        <v>0.06534923613071442</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.001699822372756898</v>
+        <v>0.04350437223911285</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.005356344860047102</v>
+        <v>0.007477010600268841</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.005537143908441067</v>
+        <v>0.04048594832420349</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.002612159354612231</v>
+        <v>0.02850626222789288</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.009652195498347282</v>
+        <v>0.05923132970929146</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.007380323018878698</v>
+        <v>0.01671076752245426</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.00473037688061595</v>
+        <v>0.1361944973468781</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.005680104717612267</v>
+        <v>0.03069387376308441</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.01839785650372505</v>
+        <v>0.1590177267789841</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.001904201693832874</v>
+        <v>0.06229656189680099</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.00479606632143259</v>
+        <v>0.1250657737255096</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.007682162802666426</v>
+        <v>0.1009470522403717</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.01478835660964251</v>
+        <v>0.1175339072942734</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.005254587158560753</v>
+        <v>0.05976373702287674</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.007317908573895693</v>
+        <v>0.07830411195755005</v>
       </c>
       <c r="AS4" t="n">
-        <v>0.007150439079850912</v>
+        <v>0.008905412629246712</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.01163229532539845</v>
+        <v>0.001838471740484238</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.0821024477481842</v>
+        <v>0.1898858994245529</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.006962832529097795</v>
+        <v>0.003910134546458721</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.01260973047465086</v>
+        <v>0.312839686870575</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.006654241587966681</v>
+        <v>0.281177818775177</v>
       </c>
       <c r="AY4" t="n">
-        <v>0.003112689359113574</v>
+        <v>0.02094301953911781</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.003470099531114101</v>
+        <v>0.02703521400690079</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.004877611994743347</v>
+        <v>0.03364808857440948</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.004003777168691158</v>
+        <v>0.1377892196178436</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.003938406705856323</v>
+        <v>0.0240622665733099</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.01063379924744368</v>
+        <v>0.007947351783514023</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.007614008150994778</v>
+        <v>0.0310848280787468</v>
       </c>
       <c r="BF4" t="n">
-        <v>0.01335657574236393</v>
+        <v>0.05225896835327148</v>
       </c>
       <c r="BG4" t="n">
-        <v>0.03853438794612885</v>
+        <v>0.06816131621599197</v>
       </c>
       <c r="BH4" t="n">
-        <v>0.005966273602098227</v>
+        <v>0.08309875428676605</v>
       </c>
       <c r="BI4" t="n">
-        <v>0.02146863006055355</v>
+        <v>0.03176186233758926</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.004744875710457563</v>
+        <v>0.02124342322349548</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.005386609584093094</v>
+        <v>0.1959489434957504</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.01884213835000992</v>
+        <v>0.00633746013045311</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.01926431432366371</v>
+        <v>0.02143485099077225</v>
       </c>
       <c r="BN4" t="n">
-        <v>0.002968068234622478</v>
+        <v>0.03873150795698166</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.009457770735025406</v>
+        <v>0.02747699618339539</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.006696125492453575</v>
+        <v>0.02069780044257641</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0.01019963435828686</v>
+        <v>0.06854548305273056</v>
       </c>
       <c r="BR4" t="n">
-        <v>0.0001836540177464485</v>
+        <v>0.003181279636919498</v>
       </c>
       <c r="BS4" t="n">
-        <v>0.004273560829460621</v>
+        <v>0.01573259755969048</v>
       </c>
       <c r="BT4" t="n">
-        <v>0.005192006938159466</v>
+        <v>0.01387200783938169</v>
       </c>
       <c r="BU4" t="n">
-        <v>0.01015041396021843</v>
+        <v>0.00751403346657753</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.04590649530291557</v>
+        <v>0.1865744143724442</v>
       </c>
       <c r="BW4" t="n">
-        <v>0.01180646847933531</v>
+        <v>0.002815017476677895</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.007003114558756351</v>
+        <v>0.2474954873323441</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.009030386805534363</v>
+        <v>0.05204350128769875</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0.02104857377707958</v>
+        <v>0.08174694329500198</v>
       </c>
       <c r="CA4" t="n">
-        <v>0.003305663354694843</v>
+        <v>0.05339831858873367</v>
       </c>
       <c r="CB4" t="n">
-        <v>0.003825972089543939</v>
+        <v>0.06206503137946129</v>
       </c>
       <c r="CC4" t="n">
-        <v>0.008045092225074768</v>
+        <v>0.003207186236977577</v>
       </c>
       <c r="CD4" t="n">
-        <v>0.006553266663104296</v>
+        <v>0.01272523030638695</v>
       </c>
       <c r="CE4" t="n">
-        <v>0.01531651336699724</v>
+        <v>0.1255687475204468</v>
       </c>
       <c r="CF4" t="n">
-        <v>0.003877675626426935</v>
+        <v>0.0006464454345405102</v>
       </c>
       <c r="CG4" t="n">
-        <v>0.006461578886955976</v>
+        <v>0.2219038307666779</v>
       </c>
       <c r="CH4" t="n">
-        <v>0.003850755514577031</v>
+        <v>0.01585780642926693</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.008437155745923519</v>
+        <v>0.003054216969758272</v>
       </c>
       <c r="CJ4" t="n">
-        <v>0.003579022828489542</v>
+        <v>0.01252125296741724</v>
       </c>
       <c r="CK4" t="n">
-        <v>0.002780783455818892</v>
+        <v>0.06235871091485023</v>
       </c>
       <c r="CL4" t="n">
-        <v>0.004996372852474451</v>
+        <v>0.01754417084157467</v>
       </c>
       <c r="CM4" t="n">
-        <v>0.01045349519699812</v>
+        <v>0.04631676524877548</v>
       </c>
       <c r="CN4" t="n">
-        <v>0.002097843680530787</v>
+        <v>0.1284356713294983</v>
       </c>
       <c r="CO4" t="n">
-        <v>0.006661099847406149</v>
+        <v>0.05905022844672203</v>
       </c>
       <c r="CP4" t="n">
-        <v>0.01235373131930828</v>
+        <v>0.3482154607772827</v>
       </c>
       <c r="CQ4" t="n">
-        <v>0.01173209398984909</v>
+        <v>0.02986176125705242</v>
       </c>
       <c r="CR4" t="n">
-        <v>0.009612571448087692</v>
+        <v>0.02398073486983776</v>
       </c>
       <c r="CS4" t="n">
-        <v>0.01419243402779102</v>
+        <v>0.002072833478450775</v>
       </c>
       <c r="CT4" t="n">
-        <v>0.02002628333866596</v>
+        <v>0.01326338574290276</v>
       </c>
       <c r="CU4" t="n">
-        <v>0.0007324555772356689</v>
+        <v>0.03568973764777184</v>
       </c>
       <c r="CV4" t="n">
-        <v>0.006906267255544662</v>
+        <v>0.01870177313685417</v>
       </c>
       <c r="CW4" t="n">
-        <v>0.01092924829572439</v>
+        <v>0.1212092936038971</v>
       </c>
       <c r="CX4" t="n">
-        <v>0.004049086477607489</v>
+        <v>0.01008079573512077</v>
       </c>
       <c r="CY4" t="n">
-        <v>0.0117964968085289</v>
+        <v>0.2308138310909271</v>
       </c>
       <c r="CZ4" t="n">
-        <v>0.0005452820332720876</v>
+        <v>0.002454007510095835</v>
       </c>
       <c r="DA4" t="n">
-        <v>0.01136114168912172</v>
+        <v>0.006719216704368591</v>
       </c>
       <c r="DB4" t="n">
-        <v>0.002468011807650328</v>
+        <v>0.03328156471252441</v>
       </c>
       <c r="DC4" t="n">
-        <v>0.002484433818608522</v>
+        <v>0.06939655542373657</v>
       </c>
       <c r="DD4" t="n">
-        <v>0.001405484043061733</v>
+        <v>0.008930809795856476</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.006445072591304779</v>
+        <v>0.01663223095238209</v>
       </c>
       <c r="DF4" t="n">
-        <v>0.01088110357522964</v>
+        <v>0.134046196937561</v>
       </c>
       <c r="DG4" t="n">
-        <v>0.004378273151814938</v>
+        <v>0.03658385202288628</v>
       </c>
       <c r="DH4" t="n">
-        <v>0.01909945532679558</v>
+        <v>0.1868374943733215</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.01051040645688772</v>
+        <v>0.1173404827713966</v>
       </c>
       <c r="DJ4" t="n">
-        <v>0.007278927601873875</v>
+        <v>0.1056156605482101</v>
       </c>
       <c r="DK4" t="n">
-        <v>0.01116767339408398</v>
+        <v>0.03733709454536438</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.009856667369604111</v>
+        <v>0.2186216562986374</v>
       </c>
       <c r="DM4" t="n">
-        <v>0.00927361287176609</v>
+        <v>0.1406755149364471</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.01473863795399666</v>
+        <v>0.06001860275864601</v>
       </c>
       <c r="DO4" t="n">
-        <v>0.006690568756312132</v>
+        <v>0.06386592984199524</v>
       </c>
       <c r="DP4" t="n">
-        <v>0.0001401549961883575</v>
+        <v>0.007159273140132427</v>
       </c>
       <c r="DQ4" t="n">
-        <v>0.005992524325847626</v>
+        <v>0.1141916215419769</v>
       </c>
       <c r="DR4" t="n">
-        <v>0.00422200933098793</v>
+        <v>0.01753808744251728</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.002440796932205558</v>
+        <v>0.01931833848357201</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.003688293043524027</v>
+        <v>0.05685078725218773</v>
       </c>
       <c r="DU4" t="n">
-        <v>0.006462622433900833</v>
+        <v>0.1009949222207069</v>
       </c>
       <c r="DV4" t="n">
-        <v>0.004429025575518608</v>
+        <v>0.2121942937374115</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.005922558717429638</v>
+        <v>0.0211931187659502</v>
       </c>
       <c r="DX4" t="n">
-        <v>0.005232014693319798</v>
+        <v>0.01580597832798958</v>
       </c>
       <c r="DY4" t="n">
-        <v>0.01632916182279587</v>
+        <v>0.07826067507266998</v>
       </c>
       <c r="DZ4" t="n">
-        <v>0.002558043226599693</v>
+        <v>0.1111292019486427</v>
       </c>
       <c r="EA4" t="n">
-        <v>0.0164536964148283</v>
+        <v>0.05158524215221405</v>
       </c>
       <c r="EB4" t="n">
-        <v>0.003657884197309613</v>
+        <v>0.04339944571256638</v>
       </c>
       <c r="EC4" t="n">
-        <v>0.002791347447782755</v>
+        <v>0.05458950996398926</v>
       </c>
       <c r="ED4" t="n">
-        <v>0.008685596287250519</v>
+        <v>0.2863896191120148</v>
       </c>
       <c r="EE4" t="n">
-        <v>0.0003570591798052192</v>
+        <v>0.1848563849925995</v>
       </c>
       <c r="EF4" t="n">
-        <v>5.865516141057014e-05</v>
+        <v>0.09499397873878479</v>
       </c>
       <c r="EG4" t="n">
-        <v>0.007154266349971294</v>
+        <v>0.09655066579580307</v>
       </c>
       <c r="EH4" t="n">
-        <v>0.0011717330198735</v>
+        <v>0.06708372384309769</v>
       </c>
       <c r="EI4" t="n">
-        <v>0.0049918033182621</v>
+        <v>0.1662475019693375</v>
       </c>
       <c r="EJ4" t="n">
-        <v>0.008918138220906258</v>
+        <v>0.02988860569894314</v>
       </c>
       <c r="EK4" t="n">
-        <v>0.005697857122868299</v>
+        <v>0.007071366999298334</v>
       </c>
       <c r="EL4" t="n">
-        <v>0.004977758042514324</v>
+        <v>0.01284028403460979</v>
       </c>
       <c r="EM4" t="n">
-        <v>0.001224922365508974</v>
+        <v>0.02920727431774139</v>
       </c>
       <c r="EN4" t="n">
-        <v>0.0004059230559505522</v>
+        <v>0.02777894586324692</v>
       </c>
       <c r="EO4" t="n">
-        <v>0.006152019836008549</v>
+        <v>0.06185176223516464</v>
       </c>
       <c r="EP4" t="n">
-        <v>0.005890280939638615</v>
+        <v>0.133261114358902</v>
       </c>
       <c r="EQ4" t="n">
-        <v>0.002246424555778503</v>
+        <v>0.07433579117059708</v>
       </c>
       <c r="ER4" t="n">
-        <v>0.01241466589272022</v>
+        <v>0.1539533585309982</v>
       </c>
       <c r="ES4" t="n">
-        <v>0.005827862303704023</v>
+        <v>0.05215703696012497</v>
       </c>
       <c r="ET4" t="n">
-        <v>0.03412847593426704</v>
+        <v>0.05738300457596779</v>
       </c>
       <c r="EU4" t="n">
-        <v>0.005082889460027218</v>
+        <v>0.06809473782777786</v>
       </c>
       <c r="EV4" t="n">
-        <v>0.009512289427220821</v>
+        <v>0.08967430889606476</v>
       </c>
       <c r="EW4" t="n">
-        <v>0.0005922000273130834</v>
+        <v>0.03153504803776741</v>
       </c>
       <c r="EX4" t="n">
-        <v>0.004635263234376907</v>
+        <v>0.02015269920229912</v>
       </c>
       <c r="EY4" t="n">
-        <v>0.0101442439481616</v>
+        <v>0.1403866857290268</v>
       </c>
       <c r="EZ4" t="n">
-        <v>0.0008448548032902181</v>
+        <v>0.006407249253243208</v>
       </c>
       <c r="FA4" t="n">
-        <v>0.01086179632693529</v>
+        <v>0.2532597184181213</v>
       </c>
       <c r="FB4" t="n">
-        <v>0.001738422550261021</v>
+        <v>0.0125694153830409</v>
       </c>
       <c r="FC4" t="n">
-        <v>0.01003752183169127</v>
+        <v>0.01019327249377966</v>
       </c>
       <c r="FD4" t="n">
-        <v>0.005004412028938532</v>
+        <v>0.01810235530138016</v>
       </c>
       <c r="FE4" t="n">
-        <v>0.003438468556851149</v>
+        <v>0.09196631610393524</v>
       </c>
       <c r="FF4" t="n">
-        <v>0.005128429736942053</v>
+        <v>0.0129585973918438</v>
       </c>
       <c r="FG4" t="n">
-        <v>0.002233737148344517</v>
+        <v>0.02481496892869473</v>
       </c>
       <c r="FH4" t="n">
-        <v>0.01190510485321283</v>
+        <v>0.0590134784579277</v>
       </c>
       <c r="FI4" t="n">
-        <v>0.005029884167015553</v>
+        <v>0.04650303721427917</v>
       </c>
       <c r="FJ4" t="n">
-        <v>0.01246772520244122</v>
+        <v>0.09488889575004578</v>
       </c>
       <c r="FK4" t="n">
-        <v>0.002798832720145583</v>
+        <v>0.03829190507531166</v>
       </c>
       <c r="FL4" t="n">
-        <v>0.002140427241101861</v>
+        <v>0.01017807051539421</v>
       </c>
       <c r="FM4" t="n">
-        <v>0.0003583270590752363</v>
+        <v>0.05887048691511154</v>
       </c>
       <c r="FN4" t="n">
-        <v>0.007277496624737978</v>
+        <v>0.04529258608818054</v>
       </c>
       <c r="FO4" t="n">
-        <v>0.0089101642370224</v>
+        <v>0.1068021357059479</v>
       </c>
       <c r="FP4" t="n">
-        <v>0.002619882579892874</v>
+        <v>0.06327291578054428</v>
       </c>
       <c r="FQ4" t="n">
-        <v>0.002328738104552031</v>
+        <v>0.2089281678199768</v>
       </c>
       <c r="FR4" t="n">
-        <v>0.001343803131021559</v>
+        <v>0.1188114732503891</v>
       </c>
       <c r="FS4" t="n">
-        <v>0.001925792312249541</v>
+        <v>0.21066614985466</v>
       </c>
       <c r="FT4" t="n">
-        <v>0.02112805843353271</v>
+        <v>0.03347007557749748</v>
       </c>
       <c r="FU4" t="n">
-        <v>0.000214637431781739</v>
+        <v>0.09802395105361938</v>
       </c>
       <c r="FV4" t="n">
-        <v>0.001441718079149723</v>
+        <v>0.03425255417823792</v>
       </c>
       <c r="FW4" t="n">
-        <v>0.008186215534806252</v>
+        <v>0.05006382614374161</v>
       </c>
       <c r="FX4" t="n">
-        <v>0.00546238012611866</v>
+        <v>0.1854136735200882</v>
       </c>
       <c r="FY4" t="n">
-        <v>0.01251313835382462</v>
+        <v>0.08026781678199768</v>
       </c>
       <c r="FZ4" t="n">
-        <v>0.004359361249953508</v>
+        <v>0.03626253455877304</v>
       </c>
       <c r="GA4" t="n">
-        <v>0.001067589037120342</v>
+        <v>0.007157610729336739</v>
       </c>
       <c r="GB4" t="n">
-        <v>0.003466981928795576</v>
+        <v>0.1412744522094727</v>
       </c>
       <c r="GC4" t="n">
-        <v>0.005584103986620903</v>
+        <v>0.1212721168994904</v>
       </c>
       <c r="GD4" t="n">
-        <v>0.01044346857815981</v>
+        <v>0.03039011545479298</v>
       </c>
       <c r="GE4" t="n">
-        <v>0.02665182761847973</v>
+        <v>0.1289093494415283</v>
       </c>
       <c r="GF4" t="n">
-        <v>0.0007183307898230851</v>
+        <v>0.09563606977462769</v>
       </c>
       <c r="GG4" t="n">
-        <v>0.0008664095657877624</v>
+        <v>0.0301754642277956</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.003038582857698202</v>
+        <v>0.0005142764421179891</v>
       </c>
       <c r="B5" t="n">
-        <v>0.04686404019594193</v>
+        <v>0.01028553862124681</v>
       </c>
       <c r="C5" t="n">
-        <v>0.009695202112197876</v>
+        <v>8.427596185356379e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0152310561388731</v>
+        <v>0.00172699405811727</v>
       </c>
       <c r="E5" t="n">
-        <v>0.06660546362400055</v>
+        <v>0.001143922563642263</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0189827773720026</v>
+        <v>0.008992711082100868</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0002169199287891388</v>
+        <v>0.00325077073648572</v>
       </c>
       <c r="H5" t="n">
-        <v>0.00284643960185349</v>
+        <v>0.002697622403502464</v>
       </c>
       <c r="I5" t="n">
-        <v>0.005176053382456303</v>
+        <v>0.002260120818391442</v>
       </c>
       <c r="J5" t="n">
-        <v>0.009726261720061302</v>
+        <v>0.0003694386687129736</v>
       </c>
       <c r="K5" t="n">
-        <v>0.03021386079490185</v>
+        <v>0.01285971514880657</v>
       </c>
       <c r="L5" t="n">
-        <v>0.005162625573575497</v>
+        <v>0.0009582851780578494</v>
       </c>
       <c r="M5" t="n">
-        <v>0.009518414735794067</v>
+        <v>0.00395328551530838</v>
       </c>
       <c r="N5" t="n">
-        <v>0.06496220082044601</v>
+        <v>0.00380018400028348</v>
       </c>
       <c r="O5" t="n">
-        <v>0.02353968098759651</v>
+        <v>0.009232044219970703</v>
       </c>
       <c r="P5" t="n">
-        <v>0.00306990509852767</v>
+        <v>0.001350557547993958</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.009828904643654823</v>
+        <v>0.0008639545412734151</v>
       </c>
       <c r="R5" t="n">
-        <v>0.00509892962872982</v>
+        <v>0.00522166769951582</v>
       </c>
       <c r="S5" t="n">
-        <v>0.002189158694818616</v>
+        <v>0.0007444457150995731</v>
       </c>
       <c r="T5" t="n">
-        <v>0.01736818253993988</v>
+        <v>0.001162916305474937</v>
       </c>
       <c r="U5" t="n">
-        <v>0.004340695682913065</v>
+        <v>0.001435576821677387</v>
       </c>
       <c r="V5" t="n">
-        <v>0.001471699681133032</v>
+        <v>0.001921172719448805</v>
       </c>
       <c r="W5" t="n">
-        <v>0.002098041120916605</v>
+        <v>0.001810863148421049</v>
       </c>
       <c r="X5" t="n">
-        <v>0.01533766090869904</v>
+        <v>0.001681057969108224</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.003669981844723225</v>
+        <v>0.0008093701908364892</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.001557337120175362</v>
+        <v>0.002197343856096268</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.0009728142758831382</v>
+        <v>9.211379801854491e-05</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.0004398003220558167</v>
+        <v>0.0006122535560280085</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.01051013730466366</v>
+        <v>0.001136828330345452</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.005601006560027599</v>
+        <v>0.001411831937730312</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.009520897641777992</v>
+        <v>0.0007873575668781996</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.001727866008877754</v>
+        <v>0.004779311362653971</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.0120160486549139</v>
+        <v>0.003046619240194559</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.01165703311562538</v>
+        <v>0.0006240311777219176</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.005692373961210251</v>
+        <v>0.005538722965866327</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.001964135328307748</v>
+        <v>0.0003363227588124573</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.004845102317631245</v>
+        <v>0.0003578657633624971</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.01558137405663729</v>
+        <v>0.001189467147924006</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.005028212442994118</v>
+        <v>0.00111440964974463</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.003436725120991468</v>
+        <v>0.0009605259401723742</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.003799137193709612</v>
+        <v>0.001764261745847762</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.005085618235170841</v>
+        <v>0.0009454234968870878</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.007077348884195089</v>
+        <v>0.001346525736153126</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.001797402976080775</v>
+        <v>0.003237403463572264</v>
       </c>
       <c r="AS5" t="n">
-        <v>0.004925927147269249</v>
+        <v>0.001095758285373449</v>
       </c>
       <c r="AT5" t="n">
-        <v>0.01435110438615084</v>
+        <v>0.001449400093406439</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.04763522744178772</v>
+        <v>0.01065143384039402</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.004825185518711805</v>
+        <v>0.001939344452694058</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.001376064028590918</v>
+        <v>6.551368278451264e-05</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.01496786624193192</v>
+        <v>0.004244718234986067</v>
       </c>
       <c r="AY5" t="n">
-        <v>0.01429654471576214</v>
+        <v>0.006891428958624601</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.00547315925359726</v>
+        <v>0.0002371126611251384</v>
       </c>
       <c r="BA5" t="n">
-        <v>0.01029127277433872</v>
+        <v>0.0003437760751694441</v>
       </c>
       <c r="BB5" t="n">
-        <v>0.007407912984490395</v>
+        <v>0.00190795143134892</v>
       </c>
       <c r="BC5" t="n">
-        <v>0.004278479609638453</v>
+        <v>0.0003636498295236379</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.001190689159557223</v>
+        <v>0.00113589980173856</v>
       </c>
       <c r="BE5" t="n">
-        <v>0.003321158234030008</v>
+        <v>0.0006071705720387399</v>
       </c>
       <c r="BF5" t="n">
-        <v>0.008723359555006027</v>
+        <v>0.001545098260976374</v>
       </c>
       <c r="BG5" t="n">
-        <v>0.04384757578372955</v>
+        <v>0.002046633278951049</v>
       </c>
       <c r="BH5" t="n">
-        <v>0.007237065117806196</v>
+        <v>0.0003245006664656103</v>
       </c>
       <c r="BI5" t="n">
-        <v>0.003341556526720524</v>
+        <v>0.001153957797214389</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.01213305909186602</v>
+        <v>0.002630895236507058</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.008330870419740677</v>
+        <v>0.001129511976614594</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.005032281391322613</v>
+        <v>0.0009403233998455107</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.01746287010610104</v>
+        <v>0.002330793999135494</v>
       </c>
       <c r="BN5" t="n">
-        <v>0.003797372803092003</v>
+        <v>3.291941175120883e-05</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.009816765785217285</v>
+        <v>1.93091036635451e-05</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.0106058856472373</v>
+        <v>0.003278098767623305</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0.01251772325485945</v>
+        <v>0.001443208777345717</v>
       </c>
       <c r="BR5" t="n">
-        <v>0.009060394018888474</v>
+        <v>0.003826363943517208</v>
       </c>
       <c r="BS5" t="n">
-        <v>0.00322028947994113</v>
+        <v>0.0001656340609770268</v>
       </c>
       <c r="BT5" t="n">
-        <v>0.00515930587425828</v>
+        <v>0.002855615224689245</v>
       </c>
       <c r="BU5" t="n">
-        <v>0.008794402703642845</v>
+        <v>0.0005738622276112437</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.02686038799583912</v>
+        <v>0.006319565232843161</v>
       </c>
       <c r="BW5" t="n">
-        <v>0.01294208317995071</v>
+        <v>0.0005843302933499217</v>
       </c>
       <c r="BX5" t="n">
-        <v>0.002588936826214194</v>
+        <v>0.002711947774514556</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.01333361491560936</v>
+        <v>0.0004172802437096834</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0.007183458656072617</v>
+        <v>0.003566137282177806</v>
       </c>
       <c r="CA5" t="n">
-        <v>0.004823334980756044</v>
+        <v>0.0006064936751499772</v>
       </c>
       <c r="CB5" t="n">
-        <v>0.002827598713338375</v>
+        <v>0.0006055095582269132</v>
       </c>
       <c r="CC5" t="n">
-        <v>0.002266163937747478</v>
+        <v>0.0002075947995763272</v>
       </c>
       <c r="CD5" t="n">
-        <v>0.001627635443583131</v>
+        <v>0.000593676813878119</v>
       </c>
       <c r="CE5" t="n">
-        <v>0.008996790274977684</v>
+        <v>0.002961482852697372</v>
       </c>
       <c r="CF5" t="n">
-        <v>0.0004694542440120131</v>
+        <v>0.0002273649006383494</v>
       </c>
       <c r="CG5" t="n">
-        <v>0.007542697712779045</v>
+        <v>0.0001883092918433249</v>
       </c>
       <c r="CH5" t="n">
-        <v>0.008150318637490273</v>
+        <v>2.501696872059256e-05</v>
       </c>
       <c r="CI5" t="n">
-        <v>0.005722520407289267</v>
+        <v>0.002420895732939243</v>
       </c>
       <c r="CJ5" t="n">
-        <v>0.005199663806706667</v>
+        <v>0.001341791823506355</v>
       </c>
       <c r="CK5" t="n">
-        <v>0.001080479705706239</v>
+        <v>0.0005607111379504204</v>
       </c>
       <c r="CL5" t="n">
-        <v>0.001530694193206728</v>
+        <v>0.000851356890052557</v>
       </c>
       <c r="CM5" t="n">
-        <v>0.015213867649436</v>
+        <v>0.0005688299424946308</v>
       </c>
       <c r="CN5" t="n">
-        <v>0.006606144830584526</v>
+        <v>0.005258269142359495</v>
       </c>
       <c r="CO5" t="n">
-        <v>0.0004782389150932431</v>
+        <v>0.001983931753784418</v>
       </c>
       <c r="CP5" t="n">
-        <v>0.004497545305639505</v>
+        <v>0.001527074608020484</v>
       </c>
       <c r="CQ5" t="n">
-        <v>0.002278157975524664</v>
+        <v>0.001356965396553278</v>
       </c>
       <c r="CR5" t="n">
-        <v>0.001483275787904859</v>
+        <v>0.0007848539971746504</v>
       </c>
       <c r="CS5" t="n">
-        <v>0.002796259010210633</v>
+        <v>0.000656462274491787</v>
       </c>
       <c r="CT5" t="n">
-        <v>0.008472676388919353</v>
+        <v>0.001109497039578855</v>
       </c>
       <c r="CU5" t="n">
-        <v>0.001450941897928715</v>
+        <v>0.001017497852444649</v>
       </c>
       <c r="CV5" t="n">
-        <v>0.001362509443424642</v>
+        <v>4.28810017183423e-05</v>
       </c>
       <c r="CW5" t="n">
-        <v>0.004914694931358099</v>
+        <v>0.002790274331346154</v>
       </c>
       <c r="CX5" t="n">
-        <v>0.001653202110901475</v>
+        <v>4.597744555212557e-05</v>
       </c>
       <c r="CY5" t="n">
-        <v>0.00961539801210165</v>
+        <v>7.451354758813977e-05</v>
       </c>
       <c r="CZ5" t="n">
-        <v>0.008138579316437244</v>
+        <v>0.000300167768727988</v>
       </c>
       <c r="DA5" t="n">
-        <v>0.007532593794167042</v>
+        <v>0.002532528014853597</v>
       </c>
       <c r="DB5" t="n">
-        <v>0.003951904829591513</v>
+        <v>0.0004837081651203334</v>
       </c>
       <c r="DC5" t="n">
-        <v>0.001108206459321082</v>
+        <v>0.0007703315932303667</v>
       </c>
       <c r="DD5" t="n">
-        <v>0.003234438830986619</v>
+        <v>0.0009392286301590502</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.00377157237380743</v>
+        <v>0.0007929691346362233</v>
       </c>
       <c r="DF5" t="n">
-        <v>0.02721975184977055</v>
+        <v>0.003871801542118192</v>
       </c>
       <c r="DG5" t="n">
-        <v>0.0007085848483256996</v>
+        <v>0.001621932489797473</v>
       </c>
       <c r="DH5" t="n">
-        <v>0.02117878757417202</v>
+        <v>0.001106892945244908</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.004875010810792446</v>
+        <v>0.002160205971449614</v>
       </c>
       <c r="DJ5" t="n">
-        <v>4.983379039913416e-05</v>
+        <v>0.002868886804208159</v>
       </c>
       <c r="DK5" t="n">
-        <v>0.01942458562552929</v>
+        <v>0.0001916601613629609</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.004490416031330824</v>
+        <v>0.001533263246528804</v>
       </c>
       <c r="DM5" t="n">
-        <v>0.00680973194539547</v>
+        <v>0.001461552223190665</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.006409989669919014</v>
+        <v>0.00184137059841305</v>
       </c>
       <c r="DO5" t="n">
-        <v>0.005197725258767605</v>
+        <v>0.001916563836857677</v>
       </c>
       <c r="DP5" t="n">
-        <v>0.001195091055706143</v>
+        <v>0.0008552782237529755</v>
       </c>
       <c r="DQ5" t="n">
-        <v>0.01251305919140577</v>
+        <v>0.00245983200147748</v>
       </c>
       <c r="DR5" t="n">
-        <v>0.001364136463962495</v>
+        <v>0.001251168549060822</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.01741041988134384</v>
+        <v>0.001644117408432066</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.003233916824683547</v>
+        <v>3.733616904355586e-05</v>
       </c>
       <c r="DU5" t="n">
-        <v>0.004904864821583033</v>
+        <v>0.002958915894851089</v>
       </c>
       <c r="DV5" t="n">
-        <v>0.002227886114269495</v>
+        <v>0.0007623872370459139</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.003555588657036424</v>
+        <v>0.001715025398880243</v>
       </c>
       <c r="DX5" t="n">
-        <v>0.0007798508158884943</v>
+        <v>0.0004325633635744452</v>
       </c>
       <c r="DY5" t="n">
-        <v>0.004801364149898291</v>
+        <v>0.001099992077797651</v>
       </c>
       <c r="DZ5" t="n">
-        <v>0.002741729374974966</v>
+        <v>0.0014750697882846</v>
       </c>
       <c r="EA5" t="n">
-        <v>0.01007783506065607</v>
+        <v>0.0001940884976647794</v>
       </c>
       <c r="EB5" t="n">
-        <v>0.008878824301064014</v>
+        <v>0.001731921220198274</v>
       </c>
       <c r="EC5" t="n">
-        <v>0.001028185477480292</v>
+        <v>0.00101060199085623</v>
       </c>
       <c r="ED5" t="n">
-        <v>0.00150391343049705</v>
+        <v>0.001819400233216584</v>
       </c>
       <c r="EE5" t="n">
-        <v>0.0002385121770203114</v>
+        <v>0.00216681114397943</v>
       </c>
       <c r="EF5" t="n">
-        <v>0.00832816120237112</v>
+        <v>0.0002928597969003022</v>
       </c>
       <c r="EG5" t="n">
-        <v>0.0002242875052616</v>
+        <v>0.0007773920660838485</v>
       </c>
       <c r="EH5" t="n">
-        <v>0.0007273980882018805</v>
+        <v>0.001352156279608607</v>
       </c>
       <c r="EI5" t="n">
-        <v>0.002957978285849094</v>
+        <v>8.09633347671479e-05</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0.009261837229132652</v>
+        <v>0.0008660937310196459</v>
       </c>
       <c r="EK5" t="n">
-        <v>0.000193958287127316</v>
+        <v>0.001364444033242762</v>
       </c>
       <c r="EL5" t="n">
-        <v>0.007145396899431944</v>
+        <v>0.001095921033993363</v>
       </c>
       <c r="EM5" t="n">
-        <v>0.001910846913233399</v>
+        <v>0.0001363232295261696</v>
       </c>
       <c r="EN5" t="n">
-        <v>0.004648784175515175</v>
+        <v>0.0001117316423915327</v>
       </c>
       <c r="EO5" t="n">
-        <v>0.006790450774133205</v>
+        <v>0.0005893514025956392</v>
       </c>
       <c r="EP5" t="n">
-        <v>0.006873070728033781</v>
+        <v>0.001302478136494756</v>
       </c>
       <c r="EQ5" t="n">
-        <v>0.007987708784639835</v>
+        <v>0.0007278479170054197</v>
       </c>
       <c r="ER5" t="n">
-        <v>0.005507903173565865</v>
+        <v>0.0001448822440579534</v>
       </c>
       <c r="ES5" t="n">
-        <v>5.095615051686764e-05</v>
+        <v>0.002022909931838512</v>
       </c>
       <c r="ET5" t="n">
-        <v>0.009865014813840389</v>
+        <v>0.002482253592461348</v>
       </c>
       <c r="EU5" t="n">
-        <v>0.0009544325293973088</v>
+        <v>0.00036297642509453</v>
       </c>
       <c r="EV5" t="n">
-        <v>0.006306687369942665</v>
+        <v>0.000645577791146934</v>
       </c>
       <c r="EW5" t="n">
-        <v>0.002242770278826356</v>
+        <v>0.0002617898862808943</v>
       </c>
       <c r="EX5" t="n">
-        <v>0.001716082799248397</v>
+        <v>0.0002231798134744167</v>
       </c>
       <c r="EY5" t="n">
-        <v>0.00365487695671618</v>
+        <v>0.003623093711212277</v>
       </c>
       <c r="EZ5" t="n">
-        <v>0.0002175746922148392</v>
+        <v>0.0001982263929676265</v>
       </c>
       <c r="FA5" t="n">
-        <v>0.008225048892199993</v>
+        <v>0.0001943378010764718</v>
       </c>
       <c r="FB5" t="n">
-        <v>0.008080700412392616</v>
+        <v>0.0003479397273622453</v>
       </c>
       <c r="FC5" t="n">
-        <v>0.007585120387375355</v>
+        <v>0.002056027296930552</v>
       </c>
       <c r="FD5" t="n">
-        <v>0.005076134577393532</v>
+        <v>0.001295760390348732</v>
       </c>
       <c r="FE5" t="n">
-        <v>0.0003166249953210354</v>
+        <v>0.0006214826134964824</v>
       </c>
       <c r="FF5" t="n">
-        <v>0.0001336620189249516</v>
+        <v>0.0001325286139035597</v>
       </c>
       <c r="FG5" t="n">
-        <v>0.008005267009139061</v>
+        <v>0.0002106527099385858</v>
       </c>
       <c r="FH5" t="n">
-        <v>0.0116894543170929</v>
+        <v>0.003333354834467173</v>
       </c>
       <c r="FI5" t="n">
-        <v>0.006210146471858025</v>
+        <v>0.002096696058288217</v>
       </c>
       <c r="FJ5" t="n">
-        <v>0.004526328295469284</v>
+        <v>0.0007837244193069637</v>
       </c>
       <c r="FK5" t="n">
-        <v>0.0004590239841490984</v>
+        <v>0.0003301346441730857</v>
       </c>
       <c r="FL5" t="n">
-        <v>0.001672741258516908</v>
+        <v>0.003237007185816765</v>
       </c>
       <c r="FM5" t="n">
-        <v>0.002504065399989486</v>
+        <v>0.001102936104871333</v>
       </c>
       <c r="FN5" t="n">
-        <v>0.004952107090502977</v>
+        <v>0.002784922253340483</v>
       </c>
       <c r="FO5" t="n">
-        <v>0.004460280761122704</v>
+        <v>0.003685912117362022</v>
       </c>
       <c r="FP5" t="n">
-        <v>0.008031044155359268</v>
+        <v>4.612794145941734e-05</v>
       </c>
       <c r="FQ5" t="n">
-        <v>0.008261575363576412</v>
+        <v>0.0006886416231282055</v>
       </c>
       <c r="FR5" t="n">
-        <v>0.003401147201657295</v>
+        <v>0.005072681233286858</v>
       </c>
       <c r="FS5" t="n">
-        <v>0.01950204931199551</v>
+        <v>0.00348813459277153</v>
       </c>
       <c r="FT5" t="n">
-        <v>0.01462504826486111</v>
+        <v>0.000975277042016387</v>
       </c>
       <c r="FU5" t="n">
-        <v>0.0004506593104451895</v>
+        <v>0.001764346612617373</v>
       </c>
       <c r="FV5" t="n">
-        <v>0.004743651486933231</v>
+        <v>0.0009420061833225191</v>
       </c>
       <c r="FW5" t="n">
-        <v>0.001864235382527113</v>
+        <v>0.004975707735866308</v>
       </c>
       <c r="FX5" t="n">
-        <v>0.001439903862774372</v>
+        <v>0.001710297074168921</v>
       </c>
       <c r="FY5" t="n">
-        <v>0.002126933075487614</v>
+        <v>0.001736834412440658</v>
       </c>
       <c r="FZ5" t="n">
-        <v>0.009371222928166389</v>
+        <v>0.0002372126618865877</v>
       </c>
       <c r="GA5" t="n">
-        <v>0.009809721261262894</v>
+        <v>0.001806244254112244</v>
       </c>
       <c r="GB5" t="n">
-        <v>0.005482817534357309</v>
+        <v>0.0006577447056770325</v>
       </c>
       <c r="GC5" t="n">
-        <v>0.001234139548614621</v>
+        <v>0.002431917702779174</v>
       </c>
       <c r="GD5" t="n">
-        <v>0.008604235947132111</v>
+        <v>0.003872831584885716</v>
       </c>
       <c r="GE5" t="n">
-        <v>0.009246963076293468</v>
+        <v>0.0002906275040004402</v>
       </c>
       <c r="GF5" t="n">
-        <v>0.01408333517611027</v>
+        <v>0.002394937910139561</v>
       </c>
       <c r="GG5" t="n">
-        <v>0.005334367975592613</v>
+        <v>0.00142752006649971</v>
       </c>
     </row>
     <row r="6">
@@ -3844,1709 +3844,5123 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.01127031724900007</v>
+        <v>0.7185078263282776</v>
       </c>
       <c r="B7" t="n">
-        <v>0.1787422895431519</v>
+        <v>1.138138890266418</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02467609196901321</v>
+        <v>0.1096626296639442</v>
       </c>
       <c r="D7" t="n">
-        <v>0.07186364382505417</v>
+        <v>0.2287607640028</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2154347151517868</v>
+        <v>0.3138230443000793</v>
       </c>
       <c r="F7" t="n">
-        <v>0.05721990764141083</v>
+        <v>0.4072443842887878</v>
       </c>
       <c r="G7" t="n">
-        <v>0.08632788062095642</v>
+        <v>0.1037675589323044</v>
       </c>
       <c r="H7" t="n">
-        <v>0.06717658042907715</v>
+        <v>0.4973543286323547</v>
       </c>
       <c r="I7" t="n">
-        <v>0.03851942718029022</v>
+        <v>0.06738343834877014</v>
       </c>
       <c r="J7" t="n">
-        <v>0.02760263904929161</v>
+        <v>0.8286593556404114</v>
       </c>
       <c r="K7" t="n">
-        <v>0.101853996515274</v>
+        <v>0.9595478177070618</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02742421254515648</v>
+        <v>0.2428258955478668</v>
       </c>
       <c r="M7" t="n">
-        <v>0.02999598532915115</v>
+        <v>0.6489530801773071</v>
       </c>
       <c r="N7" t="n">
-        <v>0.206072673201561</v>
+        <v>0.7415758967399597</v>
       </c>
       <c r="O7" t="n">
-        <v>0.06704975664615631</v>
+        <v>0.2137226760387421</v>
       </c>
       <c r="P7" t="n">
-        <v>0.08922363072633743</v>
+        <v>0.2404106706380844</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.02205640263855457</v>
+        <v>0.4532472789287567</v>
       </c>
       <c r="R7" t="n">
-        <v>0.005744604393839836</v>
+        <v>0.3318690955638885</v>
       </c>
       <c r="S7" t="n">
-        <v>0.008003104478120804</v>
+        <v>0.07045990973711014</v>
       </c>
       <c r="T7" t="n">
-        <v>0.03299202024936676</v>
+        <v>0.08571039140224457</v>
       </c>
       <c r="U7" t="n">
-        <v>0.01343872677534819</v>
+        <v>0.1503341346979141</v>
       </c>
       <c r="V7" t="n">
-        <v>0.0556640662252903</v>
+        <v>0.2143008708953857</v>
       </c>
       <c r="W7" t="n">
-        <v>0.08840593695640564</v>
+        <v>0.06699270755052567</v>
       </c>
       <c r="X7" t="n">
-        <v>0.02915611304342747</v>
+        <v>0.03848864510655403</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.01823877915740013</v>
+        <v>0.06307084113359451</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.03747865557670593</v>
+        <v>0.2065078020095825</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.0002691838890314102</v>
+        <v>0.274710476398468</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.01855164021253586</v>
+        <v>0.2763258516788483</v>
       </c>
       <c r="AC7" t="n">
-        <v>7.76930246502161e-05</v>
+        <v>0.3077569603919983</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.01072837226092815</v>
+        <v>0.01886521279811859</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.02785316482186317</v>
+        <v>0.06315037608146667</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.0273414421826601</v>
+        <v>0.02194884605705738</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.05449987947940826</v>
+        <v>0.03484386950731277</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.01774570159614086</v>
+        <v>0.09845533967018127</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.00235745171085</v>
+        <v>0.02838969603180885</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.01274852175265551</v>
+        <v>0.0146403294056654</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.02504577487707138</v>
+        <v>0.202657625079155</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.04503576830029488</v>
+        <v>0.3969701528549194</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.01432938035577536</v>
+        <v>0.3787177503108978</v>
       </c>
       <c r="AN7" t="n">
-        <v>0.01014531590044498</v>
+        <v>0.1490879356861115</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.02067449316382408</v>
+        <v>0.1965972483158112</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.03784163668751717</v>
+        <v>0.02055479027330875</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.01422374323010445</v>
+        <v>0.01473113894462585</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.01743351668119431</v>
+        <v>0.002028431743383408</v>
       </c>
       <c r="AS7" t="n">
-        <v>0.00232589291408658</v>
+        <v>0.0573854111135006</v>
       </c>
       <c r="AT7" t="n">
-        <v>0.009376462548971176</v>
+        <v>0.4531124532222748</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.1574542969465256</v>
+        <v>0.2754762172698975</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.02519023977220058</v>
+        <v>0.1620402932167053</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.02837657555937767</v>
+        <v>0.1955452710390091</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.1031272858381271</v>
+        <v>0.5004302859306335</v>
       </c>
       <c r="AY7" t="n">
-        <v>0.03674975037574768</v>
+        <v>0.04945604503154755</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.0002502715215086937</v>
+        <v>0.09500207006931305</v>
       </c>
       <c r="BA7" t="n">
-        <v>0.02095657400786877</v>
+        <v>0.004110699519515038</v>
       </c>
       <c r="BB7" t="n">
-        <v>0.004306529648602009</v>
+        <v>0.06702203303575516</v>
       </c>
       <c r="BC7" t="n">
-        <v>0.02262557670474052</v>
+        <v>0.1224335506558418</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.01418567262589931</v>
+        <v>0.3092320263385773</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.01817835494875908</v>
+        <v>0.2292546778917313</v>
       </c>
       <c r="BF7" t="n">
-        <v>0.02800748124718666</v>
+        <v>0.07541849464178085</v>
       </c>
       <c r="BG7" t="n">
-        <v>0.1044201105833054</v>
+        <v>0.01057730615139008</v>
       </c>
       <c r="BH7" t="n">
-        <v>0.002335395431146026</v>
+        <v>0.4701080322265625</v>
       </c>
       <c r="BI7" t="n">
-        <v>0.02912981435656548</v>
+        <v>0.0327393151819706</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.005019166506826878</v>
+        <v>0.1798756569623947</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.006291300989687443</v>
+        <v>0.1498860865831375</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.06317383050918579</v>
+        <v>0.1742148548364639</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.05133440345525742</v>
+        <v>0.0561395063996315</v>
       </c>
       <c r="BN7" t="n">
-        <v>0.01271230075508356</v>
+        <v>0.004063056781888008</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.0264248289167881</v>
+        <v>0.07129941880702972</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.03967663273215294</v>
+        <v>0.0356220081448555</v>
       </c>
       <c r="BQ7" t="n">
-        <v>0.02171656675636768</v>
+        <v>0.2387394309043884</v>
       </c>
       <c r="BR7" t="n">
-        <v>0.002327848225831985</v>
+        <v>0.1602338403463364</v>
       </c>
       <c r="BS7" t="n">
-        <v>0.0223339032381773</v>
+        <v>0.1082658246159554</v>
       </c>
       <c r="BT7" t="n">
-        <v>0.002965816296637058</v>
+        <v>0.005451133474707603</v>
       </c>
       <c r="BU7" t="n">
-        <v>0.03000287339091301</v>
+        <v>0.3265254199504852</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.1192387118935585</v>
+        <v>0.2040850073099136</v>
       </c>
       <c r="BW7" t="n">
-        <v>0.01904324814677238</v>
+        <v>0.2405529171228409</v>
       </c>
       <c r="BX7" t="n">
-        <v>0.01925413496792316</v>
+        <v>0.2252101600170135</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.0970262810587883</v>
+        <v>0.1540264189243317</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0.06434176117181778</v>
+        <v>0.120696559548378</v>
       </c>
       <c r="CA7" t="n">
-        <v>0.02612817659974098</v>
+        <v>0.05783673375844955</v>
       </c>
       <c r="CB7" t="n">
-        <v>0.02120778895914555</v>
+        <v>0.1368372887372971</v>
       </c>
       <c r="CC7" t="n">
-        <v>0.007644212804734707</v>
+        <v>0.1838951706886292</v>
       </c>
       <c r="CD7" t="n">
-        <v>0.02037718147039413</v>
+        <v>0.1394970417022705</v>
       </c>
       <c r="CE7" t="n">
-        <v>0.01542471814900637</v>
+        <v>0.3490341901779175</v>
       </c>
       <c r="CF7" t="n">
-        <v>0.009155945852398872</v>
+        <v>0.04968336224555969</v>
       </c>
       <c r="CG7" t="n">
-        <v>0.01343696657568216</v>
+        <v>0.1176119968295097</v>
       </c>
       <c r="CH7" t="n">
-        <v>0.03410607576370239</v>
+        <v>0.04801614955067635</v>
       </c>
       <c r="CI7" t="n">
-        <v>0.02319182641804218</v>
+        <v>0.1424064189195633</v>
       </c>
       <c r="CJ7" t="n">
-        <v>0.003683079499751329</v>
+        <v>0.06624133884906769</v>
       </c>
       <c r="CK7" t="n">
-        <v>0.00791824609041214</v>
+        <v>0.1226983219385147</v>
       </c>
       <c r="CL7" t="n">
-        <v>0.004548560362309217</v>
+        <v>0.06602980941534042</v>
       </c>
       <c r="CM7" t="n">
-        <v>0.01820738054811954</v>
+        <v>0.1154970675706863</v>
       </c>
       <c r="CN7" t="n">
-        <v>0.003510214388370514</v>
+        <v>0.2483532130718231</v>
       </c>
       <c r="CO7" t="n">
-        <v>0.01574567891657352</v>
+        <v>0.3555123507976532</v>
       </c>
       <c r="CP7" t="n">
-        <v>0.0280720442533493</v>
+        <v>0.473998486995697</v>
       </c>
       <c r="CQ7" t="n">
-        <v>0.04790839925408363</v>
+        <v>0.03541351109743118</v>
       </c>
       <c r="CR7" t="n">
-        <v>0.005856665316969156</v>
+        <v>0.3951818943023682</v>
       </c>
       <c r="CS7" t="n">
-        <v>0.05859385430812836</v>
+        <v>0.001449240371584892</v>
       </c>
       <c r="CT7" t="n">
-        <v>0.04266851767897606</v>
+        <v>0.1353968530893326</v>
       </c>
       <c r="CU7" t="n">
-        <v>0.0003283629193902016</v>
+        <v>0.02723988145589828</v>
       </c>
       <c r="CV7" t="n">
-        <v>0.02066076919436455</v>
+        <v>0.1514369547367096</v>
       </c>
       <c r="CW7" t="n">
-        <v>0.004793459549546242</v>
+        <v>0.3282614946365356</v>
       </c>
       <c r="CX7" t="n">
-        <v>0.009097275324165821</v>
+        <v>0.03857404738664627</v>
       </c>
       <c r="CY7" t="n">
-        <v>0.01705454848706722</v>
+        <v>0.1163590773940086</v>
       </c>
       <c r="CZ7" t="n">
-        <v>0.03434685617685318</v>
+        <v>0.000217796303331852</v>
       </c>
       <c r="DA7" t="n">
-        <v>0.03704265505075455</v>
+        <v>0.1407903134822845</v>
       </c>
       <c r="DB7" t="n">
-        <v>0.002546069445088506</v>
+        <v>0.08892187476158142</v>
       </c>
       <c r="DC7" t="n">
-        <v>0.006997156888246536</v>
+        <v>0.1932219415903091</v>
       </c>
       <c r="DD7" t="n">
-        <v>0.00637751491740346</v>
+        <v>0.03697212040424347</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.004999780561774969</v>
+        <v>0.01008214056491852</v>
       </c>
       <c r="DF7" t="n">
-        <v>0.02725890465080738</v>
+        <v>0.1687248349189758</v>
       </c>
       <c r="DG7" t="n">
-        <v>0.02306657657027245</v>
+        <v>0.001787416636943817</v>
       </c>
       <c r="DH7" t="n">
-        <v>0.0655171200633049</v>
+        <v>0.1165484338998795</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.02549093961715698</v>
+        <v>0.3329834640026093</v>
       </c>
       <c r="DJ7" t="n">
-        <v>0.03011951223015785</v>
+        <v>0.3372483551502228</v>
       </c>
       <c r="DK7" t="n">
-        <v>0.04842432960867882</v>
+        <v>0.1737914532423019</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.02475930750370026</v>
+        <v>0.137967050075531</v>
       </c>
       <c r="DM7" t="n">
-        <v>0.008419496938586235</v>
+        <v>0.3305306434631348</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.04713086411356926</v>
+        <v>0.0470164567232132</v>
       </c>
       <c r="DO7" t="n">
-        <v>0.01664380915462971</v>
+        <v>0.2046591937541962</v>
       </c>
       <c r="DP7" t="n">
-        <v>0.02735082618892193</v>
+        <v>0.0722394660115242</v>
       </c>
       <c r="DQ7" t="n">
-        <v>0.04728222265839577</v>
+        <v>0.09105139225721359</v>
       </c>
       <c r="DR7" t="n">
-        <v>0.03588017821311951</v>
+        <v>0.01437428779900074</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.02721840143203735</v>
+        <v>0.4014748632907867</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.004519392736256123</v>
+        <v>0.1305590718984604</v>
       </c>
       <c r="DU7" t="n">
-        <v>0.05640674009919167</v>
+        <v>0.3261962831020355</v>
       </c>
       <c r="DV7" t="n">
-        <v>0.008545604534447193</v>
+        <v>0.05427891761064529</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.00474760914221406</v>
+        <v>0.07547234743833542</v>
       </c>
       <c r="DX7" t="n">
-        <v>0.03423132002353668</v>
+        <v>0.02129821479320526</v>
       </c>
       <c r="DY7" t="n">
-        <v>0.0257920678704977</v>
+        <v>0.2322871088981628</v>
       </c>
       <c r="DZ7" t="n">
-        <v>0.001095098908990622</v>
+        <v>0.3055281043052673</v>
       </c>
       <c r="EA7" t="n">
-        <v>0.047503262758255</v>
+        <v>0.5858285427093506</v>
       </c>
       <c r="EB7" t="n">
-        <v>0.001956465886905789</v>
+        <v>0.5657141208648682</v>
       </c>
       <c r="EC7" t="n">
-        <v>0.001916998531669378</v>
+        <v>0.262854278087616</v>
       </c>
       <c r="ED7" t="n">
-        <v>0.01135152485221624</v>
+        <v>0.3006537258625031</v>
       </c>
       <c r="EE7" t="n">
-        <v>0.01982095837593079</v>
+        <v>0.1827523857355118</v>
       </c>
       <c r="EF7" t="n">
-        <v>0.002707549370825291</v>
+        <v>0.06471920013427734</v>
       </c>
       <c r="EG7" t="n">
-        <v>0.002658559940755367</v>
+        <v>0.1458078920841217</v>
       </c>
       <c r="EH7" t="n">
-        <v>0.003294095396995544</v>
+        <v>0.2706680297851562</v>
       </c>
       <c r="EI7" t="n">
-        <v>0.01688919588923454</v>
+        <v>0.05647099763154984</v>
       </c>
       <c r="EJ7" t="n">
-        <v>0.02590478211641312</v>
+        <v>0.05031564459204674</v>
       </c>
       <c r="EK7" t="n">
-        <v>0.02636745199561119</v>
+        <v>0.1184083446860313</v>
       </c>
       <c r="EL7" t="n">
-        <v>0.006176648661494255</v>
+        <v>0.006057919003069401</v>
       </c>
       <c r="EM7" t="n">
-        <v>0.01291271764785051</v>
+        <v>0.09990693628787994</v>
       </c>
       <c r="EN7" t="n">
-        <v>0.006257705856114626</v>
+        <v>0.152966633439064</v>
       </c>
       <c r="EO7" t="n">
-        <v>0.007712122052907944</v>
+        <v>0.2489490956068039</v>
       </c>
       <c r="EP7" t="n">
-        <v>0.0254931915551424</v>
+        <v>0.3391973972320557</v>
       </c>
       <c r="EQ7" t="n">
-        <v>0.006525124423205853</v>
+        <v>0.2606278359889984</v>
       </c>
       <c r="ER7" t="n">
-        <v>0.004157117567956448</v>
+        <v>0.1161669716238976</v>
       </c>
       <c r="ES7" t="n">
-        <v>0.00694056274369359</v>
+        <v>0.2184721380472183</v>
       </c>
       <c r="ET7" t="n">
-        <v>0.122730441391468</v>
+        <v>0.1465340554714203</v>
       </c>
       <c r="EU7" t="n">
-        <v>0.0007598591037094593</v>
+        <v>0.00592048792168498</v>
       </c>
       <c r="EV7" t="n">
-        <v>0.05971953272819519</v>
+        <v>0.236279621720314</v>
       </c>
       <c r="EW7" t="n">
-        <v>0.02367251366376877</v>
+        <v>0.2559663951396942</v>
       </c>
       <c r="EX7" t="n">
-        <v>0.02248877659440041</v>
+        <v>0.1846503019332886</v>
       </c>
       <c r="EY7" t="n">
-        <v>0.002796417800709605</v>
+        <v>0.3779987692832947</v>
       </c>
       <c r="EZ7" t="n">
-        <v>0.0119292214512825</v>
+        <v>0.03161055594682693</v>
       </c>
       <c r="FA7" t="n">
-        <v>0.01905849017202854</v>
+        <v>0.1620216071605682</v>
       </c>
       <c r="FB7" t="n">
-        <v>0.03990821912884712</v>
+        <v>0.04001667350530624</v>
       </c>
       <c r="FC7" t="n">
-        <v>0.03060966730117798</v>
+        <v>0.08642083406448364</v>
       </c>
       <c r="FD7" t="n">
-        <v>0.005271379835903645</v>
+        <v>0.04507479816675186</v>
       </c>
       <c r="FE7" t="n">
-        <v>0.01217364519834518</v>
+        <v>0.2296229004859924</v>
       </c>
       <c r="FF7" t="n">
-        <v>0.002257937332615256</v>
+        <v>0.001708179712295532</v>
       </c>
       <c r="FG7" t="n">
-        <v>0.004841744899749756</v>
+        <v>0.09889872372150421</v>
       </c>
       <c r="FH7" t="n">
-        <v>0.04961422458291054</v>
+        <v>0.2779779434204102</v>
       </c>
       <c r="FI7" t="n">
-        <v>0.003302952507510781</v>
+        <v>0.051832415163517</v>
       </c>
       <c r="FJ7" t="n">
-        <v>0.03773349896073341</v>
+        <v>0.1150558814406395</v>
       </c>
       <c r="FK7" t="n">
-        <v>0.001771140843629837</v>
+        <v>0.2442619353532791</v>
       </c>
       <c r="FL7" t="n">
-        <v>0.02961659245193005</v>
+        <v>0.07905378192663193</v>
       </c>
       <c r="FM7" t="n">
-        <v>0.0001121798995882273</v>
+        <v>0.1408082991838455</v>
       </c>
       <c r="FN7" t="n">
-        <v>0.009521741420030594</v>
+        <v>0.3058066070079803</v>
       </c>
       <c r="FO7" t="n">
-        <v>0.005247675813734531</v>
+        <v>0.1310047060251236</v>
       </c>
       <c r="FP7" t="n">
-        <v>0.01404793933033943</v>
+        <v>0.3009216785430908</v>
       </c>
       <c r="FQ7" t="n">
-        <v>0.002737045753747225</v>
+        <v>0.5713170170783997</v>
       </c>
       <c r="FR7" t="n">
-        <v>0.009729894809424877</v>
+        <v>0.4974857568740845</v>
       </c>
       <c r="FS7" t="n">
-        <v>0.02749933488667011</v>
+        <v>0.4287679493427277</v>
       </c>
       <c r="FT7" t="n">
-        <v>0.0765831395983696</v>
+        <v>0.3160664439201355</v>
       </c>
       <c r="FU7" t="n">
-        <v>0.0203670933842659</v>
+        <v>0.1872810870409012</v>
       </c>
       <c r="FV7" t="n">
-        <v>0.03251274675130844</v>
+        <v>0.3577264845371246</v>
       </c>
       <c r="FW7" t="n">
-        <v>0.02199503220617771</v>
+        <v>0.1457855552434921</v>
       </c>
       <c r="FX7" t="n">
-        <v>0.01878836937248707</v>
+        <v>0.1327089816331863</v>
       </c>
       <c r="FY7" t="n">
-        <v>0.002245788229629397</v>
+        <v>0.1344021260738373</v>
       </c>
       <c r="FZ7" t="n">
-        <v>0.008604382164776325</v>
+        <v>0.06878582388162613</v>
       </c>
       <c r="GA7" t="n">
-        <v>0.01953079737722874</v>
+        <v>0.06577930599451065</v>
       </c>
       <c r="GB7" t="n">
-        <v>0.02374875731766224</v>
+        <v>0.03268482908606529</v>
       </c>
       <c r="GC7" t="n">
-        <v>0.02249467931687832</v>
+        <v>0.01665550097823143</v>
       </c>
       <c r="GD7" t="n">
-        <v>0.01152848638594151</v>
+        <v>0.004498161375522614</v>
       </c>
       <c r="GE7" t="n">
-        <v>0.06682728230953217</v>
+        <v>0.01590872928500175</v>
       </c>
       <c r="GF7" t="n">
-        <v>0.01321882475167513</v>
+        <v>0.1785953938961029</v>
       </c>
       <c r="GG7" t="n">
-        <v>0.001304516568779945</v>
+        <v>0.3494413495063782</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0.2806310057640076</v>
+        <v>0</v>
       </c>
       <c r="B8" t="n">
-        <v>1.054185271263123</v>
+        <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>0.001658967230468988</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6325929164886475</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0.04628482088446617</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0.311103492975235</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0.003928326070308685</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1130766347050667</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>0.09623708575963974</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0.03342194110155106</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0.8444790840148926</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0.132951021194458</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>0.6095157265663147</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1217722594738007</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>0.3092971742153168</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>0.03326527029275894</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.1981012672185898</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.07158906012773514</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1052432358264923</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>0.008180815726518631</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>0.07454768568277359</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>0.106491930782795</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.1098922938108444</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0.005467635579407215</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.00309009850025177</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.1557289361953735</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.09806958585977554</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.14834164083004</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.006098206155002117</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.1328849792480469</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.1654810607433319</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.03893948346376419</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.06131762266159058</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.05797674134373665</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.03900321573019028</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.1310807764530182</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.1308047920465469</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.1543972492218018</v>
+        <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.06337110698223114</v>
+        <v>0</v>
       </c>
       <c r="AN8" t="n">
-        <v>0.06832906603813171</v>
+        <v>0</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.06183072179555893</v>
+        <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.07983100414276123</v>
+        <v>0</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.005553901195526123</v>
+        <v>0</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.1472046077251434</v>
+        <v>0</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.1073863655328751</v>
+        <v>0</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.2706451714038849</v>
+        <v>0</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.6207570433616638</v>
+        <v>0</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.05355852469801903</v>
+        <v>0</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.1579210162162781</v>
+        <v>0</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.06725864112377167</v>
+        <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.06108016893267632</v>
+        <v>0</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.1391007900238037</v>
+        <v>0</v>
       </c>
       <c r="BA8" t="n">
-        <v>0.09772905707359314</v>
+        <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>0.1575780510902405</v>
+        <v>0</v>
       </c>
       <c r="BC8" t="n">
-        <v>0.05778917670249939</v>
+        <v>0</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.3139473497867584</v>
+        <v>0</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.1051641032099724</v>
+        <v>0</v>
       </c>
       <c r="BF8" t="n">
-        <v>0.2360549718141556</v>
+        <v>0</v>
       </c>
       <c r="BG8" t="n">
-        <v>0.1810623854398727</v>
+        <v>0</v>
       </c>
       <c r="BH8" t="n">
-        <v>0.2328098118305206</v>
+        <v>0</v>
       </c>
       <c r="BI8" t="n">
-        <v>0.0983479768037796</v>
+        <v>0</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.153347983956337</v>
+        <v>0</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.1650329381227493</v>
+        <v>0</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.04086854681372643</v>
+        <v>0</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.0848756730556488</v>
+        <v>0</v>
       </c>
       <c r="BN8" t="n">
-        <v>0.122295044362545</v>
+        <v>0</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.2368311434984207</v>
+        <v>0</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.01264351420104504</v>
+        <v>0</v>
       </c>
       <c r="BQ8" t="n">
-        <v>0.1292901635169983</v>
+        <v>0</v>
       </c>
       <c r="BR8" t="n">
-        <v>0.007342662662267685</v>
+        <v>0</v>
       </c>
       <c r="BS8" t="n">
-        <v>0.06162088364362717</v>
+        <v>0</v>
       </c>
       <c r="BT8" t="n">
-        <v>0.07118403166532516</v>
+        <v>0</v>
       </c>
       <c r="BU8" t="n">
-        <v>0.2498947232961655</v>
+        <v>0</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.3592205345630646</v>
+        <v>0</v>
       </c>
       <c r="BW8" t="n">
-        <v>0.05480789765715599</v>
+        <v>0</v>
       </c>
       <c r="BX8" t="n">
-        <v>0.1192893385887146</v>
+        <v>0</v>
       </c>
       <c r="BY8" t="n">
-        <v>0.08917535841464996</v>
+        <v>0</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0.1216632053256035</v>
+        <v>0</v>
       </c>
       <c r="CA8" t="n">
-        <v>0.02286476641893387</v>
+        <v>0</v>
       </c>
       <c r="CB8" t="n">
-        <v>0.06516309827566147</v>
+        <v>0</v>
       </c>
       <c r="CC8" t="n">
-        <v>0.1826222985982895</v>
+        <v>0</v>
       </c>
       <c r="CD8" t="n">
-        <v>0.002222560346126556</v>
+        <v>0</v>
       </c>
       <c r="CE8" t="n">
-        <v>0.1557682454586029</v>
+        <v>0</v>
       </c>
       <c r="CF8" t="n">
-        <v>0.06141890212893486</v>
+        <v>0</v>
       </c>
       <c r="CG8" t="n">
-        <v>0.1312664747238159</v>
+        <v>0</v>
       </c>
       <c r="CH8" t="n">
-        <v>0.03892267122864723</v>
+        <v>0</v>
       </c>
       <c r="CI8" t="n">
-        <v>0.04656991735100746</v>
+        <v>0</v>
       </c>
       <c r="CJ8" t="n">
-        <v>0.06102484464645386</v>
+        <v>0</v>
       </c>
       <c r="CK8" t="n">
-        <v>0.01434393413364887</v>
+        <v>0</v>
       </c>
       <c r="CL8" t="n">
-        <v>0.0911162868142128</v>
+        <v>0</v>
       </c>
       <c r="CM8" t="n">
-        <v>0.0229848176240921</v>
+        <v>0</v>
       </c>
       <c r="CN8" t="n">
-        <v>0.08886633068323135</v>
+        <v>0</v>
       </c>
       <c r="CO8" t="n">
-        <v>0.02622223645448685</v>
+        <v>0</v>
       </c>
       <c r="CP8" t="n">
-        <v>0.0003932565450668335</v>
+        <v>0</v>
       </c>
       <c r="CQ8" t="n">
-        <v>0.03415240347385406</v>
+        <v>0</v>
       </c>
       <c r="CR8" t="n">
-        <v>0.1431717872619629</v>
+        <v>0</v>
       </c>
       <c r="CS8" t="n">
-        <v>0.2077407836914062</v>
+        <v>0</v>
       </c>
       <c r="CT8" t="n">
-        <v>0.2220339477062225</v>
+        <v>0</v>
       </c>
       <c r="CU8" t="n">
-        <v>0.04239526018500328</v>
+        <v>0</v>
       </c>
       <c r="CV8" t="n">
-        <v>0.005564425140619278</v>
+        <v>0</v>
       </c>
       <c r="CW8" t="n">
-        <v>0.1278664320707321</v>
+        <v>0</v>
       </c>
       <c r="CX8" t="n">
-        <v>0.09585427492856979</v>
+        <v>0</v>
       </c>
       <c r="CY8" t="n">
-        <v>0.1468691229820251</v>
+        <v>0</v>
       </c>
       <c r="CZ8" t="n">
-        <v>0.02657099440693855</v>
+        <v>0</v>
       </c>
       <c r="DA8" t="n">
-        <v>0.01380412839353085</v>
+        <v>0</v>
       </c>
       <c r="DB8" t="n">
-        <v>0.03929324075579643</v>
+        <v>0</v>
       </c>
       <c r="DC8" t="n">
-        <v>0.0485968329012394</v>
+        <v>0</v>
       </c>
       <c r="DD8" t="n">
-        <v>0.05580015853047371</v>
+        <v>0</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.13599693775177</v>
+        <v>0</v>
       </c>
       <c r="DF8" t="n">
-        <v>0.3955962955951691</v>
+        <v>0</v>
       </c>
       <c r="DG8" t="n">
-        <v>0.1504330933094025</v>
+        <v>0</v>
       </c>
       <c r="DH8" t="n">
-        <v>0.5252704620361328</v>
+        <v>0</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.08798447996377945</v>
+        <v>0</v>
       </c>
       <c r="DJ8" t="n">
-        <v>0.04634764418005943</v>
+        <v>0</v>
       </c>
       <c r="DK8" t="n">
-        <v>0.1771342754364014</v>
+        <v>0</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.07584442943334579</v>
+        <v>0</v>
       </c>
       <c r="DM8" t="n">
-        <v>0.05205510556697845</v>
+        <v>0</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.1417960971593857</v>
+        <v>0</v>
       </c>
       <c r="DO8" t="n">
-        <v>0.1344388723373413</v>
+        <v>0</v>
       </c>
       <c r="DP8" t="n">
-        <v>0.01877810433506966</v>
+        <v>0</v>
       </c>
       <c r="DQ8" t="n">
-        <v>0.185905784368515</v>
+        <v>0</v>
       </c>
       <c r="DR8" t="n">
-        <v>0.06759850680828094</v>
+        <v>0</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.04301192611455917</v>
+        <v>0</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.07207585871219635</v>
+        <v>0</v>
       </c>
       <c r="DU8" t="n">
-        <v>0.06464098393917084</v>
+        <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>0.07658806443214417</v>
+        <v>0</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.02803740091621876</v>
+        <v>0</v>
       </c>
       <c r="DX8" t="n">
-        <v>0.06228619441390038</v>
+        <v>0</v>
       </c>
       <c r="DY8" t="n">
-        <v>0.02686125785112381</v>
+        <v>0</v>
       </c>
       <c r="DZ8" t="n">
-        <v>0.04006027057766914</v>
+        <v>0</v>
       </c>
       <c r="EA8" t="n">
-        <v>0.05582375451922417</v>
+        <v>0</v>
       </c>
       <c r="EB8" t="n">
-        <v>0.05720029026269913</v>
+        <v>0</v>
       </c>
       <c r="EC8" t="n">
-        <v>0.0104166641831398</v>
+        <v>0</v>
       </c>
       <c r="ED8" t="n">
-        <v>0.02090140245854855</v>
+        <v>0</v>
       </c>
       <c r="EE8" t="n">
-        <v>0.2023616135120392</v>
+        <v>0</v>
       </c>
       <c r="EF8" t="n">
-        <v>0.02234139107167721</v>
+        <v>0</v>
       </c>
       <c r="EG8" t="n">
-        <v>0.1256467700004578</v>
+        <v>0</v>
       </c>
       <c r="EH8" t="n">
-        <v>0.09017544984817505</v>
+        <v>0</v>
       </c>
       <c r="EI8" t="n">
-        <v>0.07065281271934509</v>
+        <v>0</v>
       </c>
       <c r="EJ8" t="n">
-        <v>0.002083644270896912</v>
+        <v>0</v>
       </c>
       <c r="EK8" t="n">
-        <v>0.08608001470565796</v>
+        <v>0</v>
       </c>
       <c r="EL8" t="n">
-        <v>0.03474170342087746</v>
+        <v>0</v>
       </c>
       <c r="EM8" t="n">
-        <v>0.02829566039144993</v>
+        <v>0</v>
       </c>
       <c r="EN8" t="n">
-        <v>0.0386078841984272</v>
+        <v>0</v>
       </c>
       <c r="EO8" t="n">
-        <v>0.01671530678868294</v>
+        <v>0</v>
       </c>
       <c r="EP8" t="n">
-        <v>0.04126692935824394</v>
+        <v>0</v>
       </c>
       <c r="EQ8" t="n">
-        <v>0.1364777386188507</v>
+        <v>0</v>
       </c>
       <c r="ER8" t="n">
-        <v>0.1447662711143494</v>
+        <v>0</v>
       </c>
       <c r="ES8" t="n">
-        <v>0.02498700469732285</v>
+        <v>0</v>
       </c>
       <c r="ET8" t="n">
-        <v>0.2156047224998474</v>
+        <v>0</v>
       </c>
       <c r="EU8" t="n">
-        <v>0.1395402848720551</v>
+        <v>0</v>
       </c>
       <c r="EV8" t="n">
-        <v>0.03372977301478386</v>
+        <v>0</v>
       </c>
       <c r="EW8" t="n">
-        <v>0.06490560621023178</v>
+        <v>0</v>
       </c>
       <c r="EX8" t="n">
-        <v>0.008746776729822159</v>
+        <v>0</v>
       </c>
       <c r="EY8" t="n">
-        <v>0.1340865343809128</v>
+        <v>0</v>
       </c>
       <c r="EZ8" t="n">
-        <v>0.09909395128488541</v>
+        <v>0</v>
       </c>
       <c r="FA8" t="n">
-        <v>0.1127460077404976</v>
+        <v>0</v>
       </c>
       <c r="FB8" t="n">
-        <v>0.05043343082070351</v>
+        <v>0</v>
       </c>
       <c r="FC8" t="n">
-        <v>0.03347039967775345</v>
+        <v>0</v>
       </c>
       <c r="FD8" t="n">
-        <v>0.1168385595083237</v>
+        <v>0</v>
       </c>
       <c r="FE8" t="n">
-        <v>0.04615635797381401</v>
+        <v>0</v>
       </c>
       <c r="FF8" t="n">
-        <v>0.08378866314888</v>
+        <v>0</v>
       </c>
       <c r="FG8" t="n">
-        <v>0.08030629903078079</v>
+        <v>0</v>
       </c>
       <c r="FH8" t="n">
-        <v>0.1033027172088623</v>
+        <v>0</v>
       </c>
       <c r="FI8" t="n">
-        <v>0.06539007276296616</v>
+        <v>0</v>
       </c>
       <c r="FJ8" t="n">
-        <v>0.08562315255403519</v>
+        <v>0</v>
       </c>
       <c r="FK8" t="n">
-        <v>0.02187221124768257</v>
+        <v>0</v>
       </c>
       <c r="FL8" t="n">
-        <v>0.02560748904943466</v>
+        <v>0</v>
       </c>
       <c r="FM8" t="n">
-        <v>0.07855013012886047</v>
+        <v>0</v>
       </c>
       <c r="FN8" t="n">
-        <v>0.04336775466799736</v>
+        <v>0</v>
       </c>
       <c r="FO8" t="n">
-        <v>0.107585147023201</v>
+        <v>0</v>
       </c>
       <c r="FP8" t="n">
-        <v>0.0449889674782753</v>
+        <v>0</v>
       </c>
       <c r="FQ8" t="n">
-        <v>0.1960238963365555</v>
+        <v>0</v>
       </c>
       <c r="FR8" t="n">
-        <v>0.2397298067808151</v>
+        <v>0</v>
       </c>
       <c r="FS8" t="n">
-        <v>0.1060637533664703</v>
+        <v>0</v>
       </c>
       <c r="FT8" t="n">
-        <v>0.17283795773983</v>
+        <v>0</v>
       </c>
       <c r="FU8" t="n">
-        <v>0.1631085872650146</v>
+        <v>0</v>
       </c>
       <c r="FV8" t="n">
-        <v>0.04859438166022301</v>
+        <v>0</v>
       </c>
       <c r="FW8" t="n">
-        <v>0.04984759539365768</v>
+        <v>0</v>
       </c>
       <c r="FX8" t="n">
-        <v>0.1122624799609184</v>
+        <v>0</v>
       </c>
       <c r="FY8" t="n">
-        <v>0.008027330040931702</v>
+        <v>0</v>
       </c>
       <c r="FZ8" t="n">
-        <v>0.09213139861822128</v>
+        <v>0</v>
       </c>
       <c r="GA8" t="n">
-        <v>0.07439377903938293</v>
+        <v>0</v>
       </c>
       <c r="GB8" t="n">
-        <v>0.02921602502465248</v>
+        <v>0</v>
       </c>
       <c r="GC8" t="n">
-        <v>0.1822752207517624</v>
+        <v>0</v>
       </c>
       <c r="GD8" t="n">
-        <v>0.160160556435585</v>
+        <v>0</v>
       </c>
       <c r="GE8" t="n">
-        <v>0.2312882542610168</v>
+        <v>0</v>
       </c>
       <c r="GF8" t="n">
-        <v>0.08522761613130569</v>
+        <v>0</v>
       </c>
       <c r="GG8" t="n">
-        <v>0.01380222290754318</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0.1525626331567764</v>
+        <v>0.01924570649862289</v>
       </c>
       <c r="B9" t="n">
-        <v>0.1976121217012405</v>
+        <v>0.2954911589622498</v>
       </c>
       <c r="C9" t="n">
-        <v>0.09605652838945389</v>
+        <v>0.124089315533638</v>
       </c>
       <c r="D9" t="n">
-        <v>0.03487458825111389</v>
+        <v>0.03297678008675575</v>
       </c>
       <c r="E9" t="n">
-        <v>0.02868576347827911</v>
+        <v>0.01245697215199471</v>
       </c>
       <c r="F9" t="n">
-        <v>0.09943510591983795</v>
+        <v>0.3235393762588501</v>
       </c>
       <c r="G9" t="n">
-        <v>0.04201488941907883</v>
+        <v>0.06944572925567627</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0406678095459938</v>
+        <v>0.1721924394369125</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0148586044088006</v>
+        <v>0.001889761537313461</v>
       </c>
       <c r="J9" t="n">
-        <v>0.123519629240036</v>
+        <v>0.0400872603058815</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1511947214603424</v>
+        <v>0.3762637972831726</v>
       </c>
       <c r="L9" t="n">
-        <v>0.09148611128330231</v>
+        <v>0.1469788104295731</v>
       </c>
       <c r="M9" t="n">
-        <v>0.01430686935782433</v>
+        <v>0.0618857741355896</v>
       </c>
       <c r="N9" t="n">
-        <v>0.02240842767059803</v>
+        <v>0.05889773368835449</v>
       </c>
       <c r="O9" t="n">
-        <v>0.05249100923538208</v>
+        <v>0.2930373549461365</v>
       </c>
       <c r="P9" t="n">
-        <v>0.004423894919455051</v>
+        <v>0.01450585201382637</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.02800711244344711</v>
+        <v>0.03786972165107727</v>
       </c>
       <c r="R9" t="n">
-        <v>0.02176757901906967</v>
+        <v>0.03444350883364677</v>
       </c>
       <c r="S9" t="n">
-        <v>0.04662183672189713</v>
+        <v>0.009760284796357155</v>
       </c>
       <c r="T9" t="n">
-        <v>0.03294704109430313</v>
+        <v>0.07031901925802231</v>
       </c>
       <c r="U9" t="n">
-        <v>0.01147111877799034</v>
+        <v>0.02066738530993462</v>
       </c>
       <c r="V9" t="n">
-        <v>0.03060682117938995</v>
+        <v>0.08698491007089615</v>
       </c>
       <c r="W9" t="n">
-        <v>0.1131426021456718</v>
+        <v>0.06148608773946762</v>
       </c>
       <c r="X9" t="n">
-        <v>0.03169947117567062</v>
+        <v>0.01679323054850101</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.03623010590672493</v>
+        <v>0.02099003084003925</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.02902326360344887</v>
+        <v>0.03522300720214844</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.008626761846244335</v>
+        <v>0.02300605177879333</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.009553888812661171</v>
+        <v>0.04985075071454048</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.007766646333038807</v>
+        <v>0.01916276663541794</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.02365963906049728</v>
+        <v>0.04917772486805916</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.02445395663380623</v>
+        <v>0.02223264053463936</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.02302108518779278</v>
+        <v>0.1152983754873276</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.01961847208440304</v>
+        <v>0.00444992259144783</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.004995652008801699</v>
+        <v>0.006591014564037323</v>
       </c>
       <c r="AI9" t="n">
-        <v>0.006402391940355301</v>
+        <v>0.1609994173049927</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.01372268982231617</v>
+        <v>0.01423831656575203</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.01023345999419689</v>
+        <v>0.003164147958159447</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.04583348333835602</v>
+        <v>0.06887452304363251</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.009733045473694801</v>
+        <v>0.004283689428120852</v>
       </c>
       <c r="AN9" t="n">
-        <v>0.03262325376272202</v>
+        <v>0.07326629757881165</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.04566163942217827</v>
+        <v>0.01771608367562294</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.05116154626011848</v>
+        <v>0.03923522308468819</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.01923537626862526</v>
+        <v>0.008513188920915127</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.00866331160068512</v>
+        <v>0.1172107681632042</v>
       </c>
       <c r="AS9" t="n">
-        <v>5.753710865974426e-06</v>
+        <v>0.005755569320172071</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.02409656345844269</v>
+        <v>0.011533347889781</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.04545172303915024</v>
+        <v>0.4680565595626831</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.003216550219804049</v>
+        <v>0.07027680426836014</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.0460473969578743</v>
+        <v>0.02949481830000877</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.06186451017856598</v>
+        <v>0.000695731258019805</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.1444979310035706</v>
+        <v>0.1293497085571289</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.01970991678535938</v>
+        <v>0.02996698766946793</v>
       </c>
       <c r="BA9" t="n">
-        <v>0.02850445546209812</v>
+        <v>0.05717413872480392</v>
       </c>
       <c r="BB9" t="n">
-        <v>0.0180845782160759</v>
+        <v>0.08027258515357971</v>
       </c>
       <c r="BC9" t="n">
-        <v>0.04622753709554672</v>
+        <v>0.01760745979845524</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.04996991902589798</v>
+        <v>0.104395680129528</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.009930058382451534</v>
+        <v>0.04581674933433533</v>
       </c>
       <c r="BF9" t="n">
-        <v>0.009181048721075058</v>
+        <v>0.00850285217165947</v>
       </c>
       <c r="BG9" t="n">
-        <v>0.0713750422000885</v>
+        <v>0.1008419245481491</v>
       </c>
       <c r="BH9" t="n">
-        <v>0.02338412590324879</v>
+        <v>0.04828118532896042</v>
       </c>
       <c r="BI9" t="n">
-        <v>0.0126604437828064</v>
+        <v>0.04506323859095573</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.01589241065084934</v>
+        <v>0.009251115843653679</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.003098680870607495</v>
+        <v>0.02634137496352196</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.01340938825160265</v>
+        <v>0.02335650660097599</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.08726511895656586</v>
+        <v>0.07909910380840302</v>
       </c>
       <c r="BN9" t="n">
-        <v>0.04390113428235054</v>
+        <v>0.05139064788818359</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.04997935146093369</v>
+        <v>0.01904615201056004</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.1066703423857689</v>
+        <v>0.07446590065956116</v>
       </c>
       <c r="BQ9" t="n">
-        <v>0.0127964923158288</v>
+        <v>0.09022946655750275</v>
       </c>
       <c r="BR9" t="n">
-        <v>0.01645180210471153</v>
+        <v>0.08430191874504089</v>
       </c>
       <c r="BS9" t="n">
-        <v>0.08068440109491348</v>
+        <v>0.05400814116001129</v>
       </c>
       <c r="BT9" t="n">
-        <v>0.005056963767856359</v>
+        <v>0.02635500952601433</v>
       </c>
       <c r="BU9" t="n">
-        <v>0.0161768663674593</v>
+        <v>0.03267307952046394</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.03277073055505753</v>
+        <v>0.3269108533859253</v>
       </c>
       <c r="BW9" t="n">
-        <v>0.005555727519094944</v>
+        <v>0.00293193943798542</v>
       </c>
       <c r="BX9" t="n">
-        <v>0.03569761291146278</v>
+        <v>0.13161401450634</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.03590252622961998</v>
+        <v>0.01701706275343895</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0.06038171797990799</v>
+        <v>0.0974026694893837</v>
       </c>
       <c r="CA9" t="n">
-        <v>0.002146807964891195</v>
+        <v>0.03773153945803642</v>
       </c>
       <c r="CB9" t="n">
-        <v>0.00297645665705204</v>
+        <v>0.02003222703933716</v>
       </c>
       <c r="CC9" t="n">
-        <v>0.01523171924054623</v>
+        <v>0.003259738907217979</v>
       </c>
       <c r="CD9" t="n">
-        <v>0.02926744520664215</v>
+        <v>0.01553601678460836</v>
       </c>
       <c r="CE9" t="n">
-        <v>0.02969344146549702</v>
+        <v>0.09174031019210815</v>
       </c>
       <c r="CF9" t="n">
-        <v>0.04130487516522408</v>
+        <v>0.02572495490312576</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.04447834938764572</v>
+        <v>0.001763202250003815</v>
       </c>
       <c r="CH9" t="n">
-        <v>0.005711689591407776</v>
+        <v>0.01232735812664032</v>
       </c>
       <c r="CI9" t="n">
-        <v>0.03767949342727661</v>
+        <v>0.07760957628488541</v>
       </c>
       <c r="CJ9" t="n">
-        <v>0.007927808910608292</v>
+        <v>0.01449710410088301</v>
       </c>
       <c r="CK9" t="n">
-        <v>0.007564932573586702</v>
+        <v>0.02426151558756828</v>
       </c>
       <c r="CL9" t="n">
-        <v>0.001280299387872219</v>
+        <v>0.0001595662906765938</v>
       </c>
       <c r="CM9" t="n">
-        <v>0.001444971188902855</v>
+        <v>0.04822215437889099</v>
       </c>
       <c r="CN9" t="n">
-        <v>0.03407182171940804</v>
+        <v>0.1967436075210571</v>
       </c>
       <c r="CO9" t="n">
-        <v>0.01647092960774899</v>
+        <v>0.01216218434274197</v>
       </c>
       <c r="CP9" t="n">
-        <v>0.124410517513752</v>
+        <v>0.03527484089136124</v>
       </c>
       <c r="CQ9" t="n">
-        <v>0.08357143402099609</v>
+        <v>0.0902760848402977</v>
       </c>
       <c r="CR9" t="n">
-        <v>0.05823551863431931</v>
+        <v>0.05187367275357246</v>
       </c>
       <c r="CS9" t="n">
-        <v>0.0596710629761219</v>
+        <v>0.0110585018992424</v>
       </c>
       <c r="CT9" t="n">
-        <v>0.03583298996090889</v>
+        <v>0.07886733114719391</v>
       </c>
       <c r="CU9" t="n">
-        <v>0.007206885144114494</v>
+        <v>0.002373331226408482</v>
       </c>
       <c r="CV9" t="n">
-        <v>0.03732531517744064</v>
+        <v>0.008575599640607834</v>
       </c>
       <c r="CW9" t="n">
-        <v>0.03335418179631233</v>
+        <v>0.08267247676849365</v>
       </c>
       <c r="CX9" t="n">
-        <v>0.03132855892181396</v>
+        <v>0.03307212889194489</v>
       </c>
       <c r="CY9" t="n">
-        <v>0.03529985621571541</v>
+        <v>0.005807011388242245</v>
       </c>
       <c r="CZ9" t="n">
-        <v>0.009731746278703213</v>
+        <v>0.006626203656196594</v>
       </c>
       <c r="DA9" t="n">
-        <v>0.009895220398902893</v>
+        <v>0.07280388474464417</v>
       </c>
       <c r="DB9" t="n">
-        <v>0.006716395728290081</v>
+        <v>0.0002047549933195114</v>
       </c>
       <c r="DC9" t="n">
-        <v>0.006021608132869005</v>
+        <v>0.01870556548237801</v>
       </c>
       <c r="DD9" t="n">
-        <v>0.00028227549046278</v>
+        <v>0.001969343284144998</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.1145849451422691</v>
+        <v>0.03367851674556732</v>
       </c>
       <c r="DF9" t="n">
-        <v>0.1076350957155228</v>
+        <v>0.1649858057498932</v>
       </c>
       <c r="DG9" t="n">
-        <v>0.01001894008368254</v>
+        <v>0.04422580823302269</v>
       </c>
       <c r="DH9" t="n">
-        <v>0.01137293968349695</v>
+        <v>0.05554892122745514</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.1452770084142685</v>
+        <v>0.06877632439136505</v>
       </c>
       <c r="DJ9" t="n">
-        <v>0.008843312039971352</v>
+        <v>0.1411829888820648</v>
       </c>
       <c r="DK9" t="n">
-        <v>0.07837433367967606</v>
+        <v>0.01605856791138649</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.06618393957614899</v>
+        <v>0.0844142884016037</v>
       </c>
       <c r="DM9" t="n">
-        <v>0.003124125534668565</v>
+        <v>0.1325777173042297</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.06978753954172134</v>
+        <v>0.02670907601714134</v>
       </c>
       <c r="DO9" t="n">
-        <v>0.03058571182191372</v>
+        <v>0.05204624310135841</v>
       </c>
       <c r="DP9" t="n">
-        <v>0.04084122180938721</v>
+        <v>0.02881544642150402</v>
       </c>
       <c r="DQ9" t="n">
-        <v>0.0698302835226059</v>
+        <v>0.0916401669383049</v>
       </c>
       <c r="DR9" t="n">
-        <v>0.03501283377408981</v>
+        <v>0.01219857670366764</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.04809288308024406</v>
+        <v>0.03004948794841766</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.0112942224368453</v>
+        <v>0.005599359050393105</v>
       </c>
       <c r="DU9" t="n">
-        <v>0.0007779886946082115</v>
+        <v>0.04677381739020348</v>
       </c>
       <c r="DV9" t="n">
-        <v>0.001610899809747934</v>
+        <v>0.001864281482994556</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.01674171909689903</v>
+        <v>0.04141338169574738</v>
       </c>
       <c r="DX9" t="n">
-        <v>0.01513175014406443</v>
+        <v>0.01617191731929779</v>
       </c>
       <c r="DY9" t="n">
-        <v>0.007235032506287098</v>
+        <v>0.05451630428433418</v>
       </c>
       <c r="DZ9" t="n">
-        <v>0.01006827224045992</v>
+        <v>0.02806731872260571</v>
       </c>
       <c r="EA9" t="n">
-        <v>0.01051582489162683</v>
+        <v>0.07540255784988403</v>
       </c>
       <c r="EB9" t="n">
-        <v>0.01175419799983501</v>
+        <v>0.01781801320612431</v>
       </c>
       <c r="EC9" t="n">
-        <v>0.01133732218295336</v>
+        <v>0.004407229833304882</v>
       </c>
       <c r="ED9" t="n">
-        <v>0.04495376348495483</v>
+        <v>0.001211896538734436</v>
       </c>
       <c r="EE9" t="n">
-        <v>0.02593720145523548</v>
+        <v>0.1267712116241455</v>
       </c>
       <c r="EF9" t="n">
-        <v>0.03444990143179893</v>
+        <v>0.0359666608273983</v>
       </c>
       <c r="EG9" t="n">
-        <v>0.02754423022270203</v>
+        <v>0.04829404503107071</v>
       </c>
       <c r="EH9" t="n">
-        <v>0.02159163542091846</v>
+        <v>0.008014600723981857</v>
       </c>
       <c r="EI9" t="n">
-        <v>0.002841818146407604</v>
+        <v>0.0241122655570507</v>
       </c>
       <c r="EJ9" t="n">
-        <v>0.02765241265296936</v>
+        <v>0.01439816784113646</v>
       </c>
       <c r="EK9" t="n">
-        <v>0.01494487188756466</v>
+        <v>0.02673527225852013</v>
       </c>
       <c r="EL9" t="n">
-        <v>0.03122576326131821</v>
+        <v>0.008837086148560047</v>
       </c>
       <c r="EM9" t="n">
-        <v>0.006044531241059303</v>
+        <v>0.01502115931361914</v>
       </c>
       <c r="EN9" t="n">
-        <v>0.00622022058814764</v>
+        <v>0.007266340777277946</v>
       </c>
       <c r="EO9" t="n">
-        <v>0.04772848635911942</v>
+        <v>0.01434281840920448</v>
       </c>
       <c r="EP9" t="n">
-        <v>0.01169829443097115</v>
+        <v>0.03880754113197327</v>
       </c>
       <c r="EQ9" t="n">
-        <v>0.08803808689117432</v>
+        <v>0.02752614952623844</v>
       </c>
       <c r="ER9" t="n">
-        <v>0.04413796588778496</v>
+        <v>0.03213314339518547</v>
       </c>
       <c r="ES9" t="n">
-        <v>0.03297294676303864</v>
+        <v>0.1216040924191475</v>
       </c>
       <c r="ET9" t="n">
-        <v>0.004035203251987696</v>
+        <v>0.1139044463634491</v>
       </c>
       <c r="EU9" t="n">
-        <v>0.01600596867501736</v>
+        <v>0.02542656287550926</v>
       </c>
       <c r="EV9" t="n">
-        <v>0.02562186494469643</v>
+        <v>0.003242592327296734</v>
       </c>
       <c r="EW9" t="n">
-        <v>0.01260552369058132</v>
+        <v>0.008013524115085602</v>
       </c>
       <c r="EX9" t="n">
-        <v>0.04408684000372887</v>
+        <v>0.0004372699186205864</v>
       </c>
       <c r="EY9" t="n">
-        <v>0.04318910092115402</v>
+        <v>0.1122288554906845</v>
       </c>
       <c r="EZ9" t="n">
-        <v>0.03677250817418098</v>
+        <v>0.02578261122107506</v>
       </c>
       <c r="FA9" t="n">
-        <v>0.04198786616325378</v>
+        <v>0.004890590906143188</v>
       </c>
       <c r="FB9" t="n">
-        <v>0.01205610670149326</v>
+        <v>0.008227442391216755</v>
       </c>
       <c r="FC9" t="n">
-        <v>0.02825626917183399</v>
+        <v>0.08069545775651932</v>
       </c>
       <c r="FD9" t="n">
-        <v>0.0006519462913274765</v>
+        <v>0.02219180949032307</v>
       </c>
       <c r="FE9" t="n">
-        <v>0.008917786180973053</v>
+        <v>0.01505346596240997</v>
       </c>
       <c r="FF9" t="n">
-        <v>0.001955376239493489</v>
+        <v>0.02219347283244133</v>
       </c>
       <c r="FG9" t="n">
-        <v>0.001523434882983565</v>
+        <v>0.01846348494291306</v>
       </c>
       <c r="FH9" t="n">
-        <v>0.01554588414728642</v>
+        <v>0.08890720456838608</v>
       </c>
       <c r="FI9" t="n">
-        <v>0.03959255665540695</v>
+        <v>0.05290365964174271</v>
       </c>
       <c r="FJ9" t="n">
-        <v>0.003338165581226349</v>
+        <v>0.05815419554710388</v>
       </c>
       <c r="FK9" t="n">
-        <v>0.01673906669020653</v>
+        <v>0.0198986679315567</v>
       </c>
       <c r="FL9" t="n">
-        <v>0.003640887327492237</v>
+        <v>0.07487484067678452</v>
       </c>
       <c r="FM9" t="n">
-        <v>0.008214570581912994</v>
+        <v>0.03366835042834282</v>
       </c>
       <c r="FN9" t="n">
-        <v>0.005869208835065365</v>
+        <v>0.1508431881666183</v>
       </c>
       <c r="FO9" t="n">
-        <v>0.006230505649000406</v>
+        <v>0.06322043389081955</v>
       </c>
       <c r="FP9" t="n">
-        <v>0.01445755176246166</v>
+        <v>0.03943254053592682</v>
       </c>
       <c r="FQ9" t="n">
-        <v>0.03542895242571831</v>
+        <v>0.02040139958262444</v>
       </c>
       <c r="FR9" t="n">
-        <v>0.06531719118356705</v>
+        <v>0.01988508924841881</v>
       </c>
       <c r="FS9" t="n">
-        <v>0.003806549124419689</v>
+        <v>0.110872395336628</v>
       </c>
       <c r="FT9" t="n">
-        <v>0.006440849509090185</v>
+        <v>0.04043816775083542</v>
       </c>
       <c r="FU9" t="n">
-        <v>0.03945976495742798</v>
+        <v>0.05923032015562057</v>
       </c>
       <c r="FV9" t="n">
-        <v>0.001562054501846433</v>
+        <v>0.07510267943143845</v>
       </c>
       <c r="FW9" t="n">
-        <v>0.03595159202814102</v>
+        <v>0.138374075293541</v>
       </c>
       <c r="FX9" t="n">
-        <v>0.01198435761034489</v>
+        <v>0.01897784322500229</v>
       </c>
       <c r="FY9" t="n">
-        <v>0.06997360289096832</v>
+        <v>0.04767001420259476</v>
       </c>
       <c r="FZ9" t="n">
-        <v>0.0008903658017516136</v>
+        <v>0.0343949943780899</v>
       </c>
       <c r="GA9" t="n">
-        <v>0.02819668687880039</v>
+        <v>0.07371699810028076</v>
       </c>
       <c r="GB9" t="n">
-        <v>0.1689209938049316</v>
+        <v>0.0136645482853055</v>
       </c>
       <c r="GC9" t="n">
-        <v>0.1903779208660126</v>
+        <v>0.0657854899764061</v>
       </c>
       <c r="GD9" t="n">
-        <v>0.05546128377318382</v>
+        <v>0.03141138702630997</v>
       </c>
       <c r="GE9" t="n">
-        <v>0.04319527745246887</v>
+        <v>0.03487904742360115</v>
       </c>
       <c r="GF9" t="n">
-        <v>0.003115026745945215</v>
+        <v>0.04148713126778603</v>
       </c>
       <c r="GG9" t="n">
-        <v>0.0160301998257637</v>
+        <v>0.02260211110115051</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>0.2584749758243561</v>
+      </c>
+      <c r="B10" t="n">
+        <v>0.8207921981811523</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.2531161308288574</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.008482656441628933</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.09304238110780716</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.3000035881996155</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.05191816762089729</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.1157557889819145</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.2185303717851639</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.1978146731853485</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.8748338222503662</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.3000082969665527</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.08046439290046692</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.2039164900779724</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.0919090062379837</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.08953793346881866</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.04818404465913773</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.2605045735836029</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.0347425676882267</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0.09877786785364151</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0.01573189534246922</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0.09841261804103851</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0.01698673143982887</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0.06689143925905228</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0.01676560938358307</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0.06855128705501556</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0.139231875538826</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.1902177333831787</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0.04930891096591949</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0.06335826963186264</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0.1649360507726669</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0.00990411639213562</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0.06953038275241852</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0.02630370482802391</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0.03556354343891144</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0.01370136812329292</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0.06464479863643646</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0.257477194070816</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0.0355726033449173</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>0.06944763660430908</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0.3619738519191742</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>0.004917562939226627</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0.05740991979837418</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>0.1125896349549294</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>0.08495064079761505</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>0.2342455089092255</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>0.4950882792472839</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>0.01211509667336941</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>0.07177062332630157</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>0.058816809207201</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>0.02050751075148582</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>0.04480370879173279</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>0.009633291512727737</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>0.006420303136110306</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>5.945935845375061e-05</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>0.00287429615855217</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>0.2468185424804688</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>0.007073819637298584</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>0.2816170454025269</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>0.2373522818088531</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>0.00584687851369381</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>0.0690942108631134</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>0.08225578814744949</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>0.010357316583395</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>0.2398247867822647</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>0.03023151308298111</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>0.1231140419840813</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>0.1256931573152542</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>0.07836828380823135</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>0.0647503063082695</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>0.04052167013287544</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>0.09927965700626373</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>0.01862107217311859</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>0.4329785704612732</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>0.07510139048099518</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>0.1130167245864868</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>0.0406162440776825</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>0.02815454453229904</v>
+      </c>
+      <c r="CA10" t="n">
+        <v>0.00618739752098918</v>
+      </c>
+      <c r="CB10" t="n">
+        <v>0.01463066041469574</v>
+      </c>
+      <c r="CC10" t="n">
+        <v>0.1300832182168961</v>
+      </c>
+      <c r="CD10" t="n">
+        <v>0.03413223102688789</v>
+      </c>
+      <c r="CE10" t="n">
+        <v>0.2888548970222473</v>
+      </c>
+      <c r="CF10" t="n">
+        <v>0.02945351600646973</v>
+      </c>
+      <c r="CG10" t="n">
+        <v>0.008724143728613853</v>
+      </c>
+      <c r="CH10" t="n">
+        <v>0.05346490070223808</v>
+      </c>
+      <c r="CI10" t="n">
+        <v>0.06602653861045837</v>
+      </c>
+      <c r="CJ10" t="n">
+        <v>0.001238095457665622</v>
+      </c>
+      <c r="CK10" t="n">
+        <v>0.04227528348565102</v>
+      </c>
+      <c r="CL10" t="n">
+        <v>0.02105425298213959</v>
+      </c>
+      <c r="CM10" t="n">
+        <v>0.08109140396118164</v>
+      </c>
+      <c r="CN10" t="n">
+        <v>0.2876717448234558</v>
+      </c>
+      <c r="CO10" t="n">
+        <v>0.1728586554527283</v>
+      </c>
+      <c r="CP10" t="n">
+        <v>0.1897712051868439</v>
+      </c>
+      <c r="CQ10" t="n">
+        <v>0.1279541552066803</v>
+      </c>
+      <c r="CR10" t="n">
+        <v>0.06278111040592194</v>
+      </c>
+      <c r="CS10" t="n">
+        <v>0.006873439997434616</v>
+      </c>
+      <c r="CT10" t="n">
+        <v>0.1101944148540497</v>
+      </c>
+      <c r="CU10" t="n">
+        <v>0.06313452124595642</v>
+      </c>
+      <c r="CV10" t="n">
+        <v>0.006995841860771179</v>
+      </c>
+      <c r="CW10" t="n">
+        <v>0.2776518166065216</v>
+      </c>
+      <c r="CX10" t="n">
+        <v>0.05091507732868195</v>
+      </c>
+      <c r="CY10" t="n">
+        <v>0.01016352139413357</v>
+      </c>
+      <c r="CZ10" t="n">
+        <v>0.02679935097694397</v>
+      </c>
+      <c r="DA10" t="n">
+        <v>0.07227141410112381</v>
+      </c>
+      <c r="DB10" t="n">
+        <v>0.002293814904987812</v>
+      </c>
+      <c r="DC10" t="n">
+        <v>0.03446097671985626</v>
+      </c>
+      <c r="DD10" t="n">
+        <v>0.05659950152039528</v>
+      </c>
+      <c r="DE10" t="n">
+        <v>0.03720749169588089</v>
+      </c>
+      <c r="DF10" t="n">
+        <v>0.2029174268245697</v>
+      </c>
+      <c r="DG10" t="n">
+        <v>0.02908047288656235</v>
+      </c>
+      <c r="DH10" t="n">
+        <v>0.02670363150537014</v>
+      </c>
+      <c r="DI10" t="n">
+        <v>0.1613670885562897</v>
+      </c>
+      <c r="DJ10" t="n">
+        <v>0.151603102684021</v>
+      </c>
+      <c r="DK10" t="n">
+        <v>0.08480163663625717</v>
+      </c>
+      <c r="DL10" t="n">
+        <v>0.1651540100574493</v>
+      </c>
+      <c r="DM10" t="n">
+        <v>0.03469623625278473</v>
+      </c>
+      <c r="DN10" t="n">
+        <v>0.1186524704098701</v>
+      </c>
+      <c r="DO10" t="n">
+        <v>0.1139464601874352</v>
+      </c>
+      <c r="DP10" t="n">
+        <v>0.04794370383024216</v>
+      </c>
+      <c r="DQ10" t="n">
+        <v>0.1113772243261337</v>
+      </c>
+      <c r="DR10" t="n">
+        <v>0.01802926510572433</v>
+      </c>
+      <c r="DS10" t="n">
+        <v>0.1310770809650421</v>
+      </c>
+      <c r="DT10" t="n">
+        <v>0.01332413032650948</v>
+      </c>
+      <c r="DU10" t="n">
+        <v>0.01010462455451488</v>
+      </c>
+      <c r="DV10" t="n">
+        <v>0.0438598059117794</v>
+      </c>
+      <c r="DW10" t="n">
+        <v>0.1317755877971649</v>
+      </c>
+      <c r="DX10" t="n">
+        <v>0.1199214309453964</v>
+      </c>
+      <c r="DY10" t="n">
+        <v>0.1111082434654236</v>
+      </c>
+      <c r="DZ10" t="n">
+        <v>0.03099763952195644</v>
+      </c>
+      <c r="EA10" t="n">
+        <v>0.2658136785030365</v>
+      </c>
+      <c r="EB10" t="n">
+        <v>0.1706307232379913</v>
+      </c>
+      <c r="EC10" t="n">
+        <v>0.05473696067929268</v>
+      </c>
+      <c r="ED10" t="n">
+        <v>0.04357098788022995</v>
+      </c>
+      <c r="EE10" t="n">
+        <v>0.2137917429208755</v>
+      </c>
+      <c r="EF10" t="n">
+        <v>0.02775949984788895</v>
+      </c>
+      <c r="EG10" t="n">
+        <v>0.2054908871650696</v>
+      </c>
+      <c r="EH10" t="n">
+        <v>0.08787710219621658</v>
+      </c>
+      <c r="EI10" t="n">
+        <v>0.09268511086702347</v>
+      </c>
+      <c r="EJ10" t="n">
+        <v>0.04393745958805084</v>
+      </c>
+      <c r="EK10" t="n">
+        <v>0.07547749578952789</v>
+      </c>
+      <c r="EL10" t="n">
+        <v>0.01080885902047157</v>
+      </c>
+      <c r="EM10" t="n">
+        <v>0.01138142216950655</v>
+      </c>
+      <c r="EN10" t="n">
+        <v>0.002709373831748962</v>
+      </c>
+      <c r="EO10" t="n">
+        <v>0.07447079569101334</v>
+      </c>
+      <c r="EP10" t="n">
+        <v>0.1524131894111633</v>
+      </c>
+      <c r="EQ10" t="n">
+        <v>0.03458765894174576</v>
+      </c>
+      <c r="ER10" t="n">
+        <v>0.09099708497524261</v>
+      </c>
+      <c r="ES10" t="n">
+        <v>0.02065237239003181</v>
+      </c>
+      <c r="ET10" t="n">
+        <v>0.03340672701597214</v>
+      </c>
+      <c r="EU10" t="n">
+        <v>0.05062786862254143</v>
+      </c>
+      <c r="EV10" t="n">
+        <v>0.05797429755330086</v>
+      </c>
+      <c r="EW10" t="n">
+        <v>0.1220892816781998</v>
+      </c>
+      <c r="EX10" t="n">
+        <v>0.04596136882901192</v>
+      </c>
+      <c r="EY10" t="n">
+        <v>0.3007694482803345</v>
+      </c>
+      <c r="EZ10" t="n">
+        <v>0.04125333577394485</v>
+      </c>
+      <c r="FA10" t="n">
+        <v>0.02326311729848385</v>
+      </c>
+      <c r="FB10" t="n">
+        <v>0.03468627110123634</v>
+      </c>
+      <c r="FC10" t="n">
+        <v>0.06054220348596573</v>
+      </c>
+      <c r="FD10" t="n">
+        <v>0.00538989994674921</v>
+      </c>
+      <c r="FE10" t="n">
+        <v>0.06358928978443146</v>
+      </c>
+      <c r="FF10" t="n">
+        <v>0.04951700568199158</v>
+      </c>
+      <c r="FG10" t="n">
+        <v>0.01176834106445312</v>
+      </c>
+      <c r="FH10" t="n">
+        <v>0.2020760774612427</v>
+      </c>
+      <c r="FI10" t="n">
+        <v>0.04810847342014313</v>
+      </c>
+      <c r="FJ10" t="n">
+        <v>0.06014946848154068</v>
+      </c>
+      <c r="FK10" t="n">
+        <v>0.1251642554998398</v>
+      </c>
+      <c r="FL10" t="n">
+        <v>0.05768829584121704</v>
+      </c>
+      <c r="FM10" t="n">
+        <v>0.08800089359283447</v>
+      </c>
+      <c r="FN10" t="n">
+        <v>0.1236836314201355</v>
+      </c>
+      <c r="FO10" t="n">
+        <v>0.09126047790050507</v>
+      </c>
+      <c r="FP10" t="n">
+        <v>0.03970393911004066</v>
+      </c>
+      <c r="FQ10" t="n">
+        <v>0.3722518384456635</v>
+      </c>
+      <c r="FR10" t="n">
+        <v>0.006069198250770569</v>
+      </c>
+      <c r="FS10" t="n">
+        <v>0.2310629636049271</v>
+      </c>
+      <c r="FT10" t="n">
+        <v>0.1178195029497147</v>
+      </c>
+      <c r="FU10" t="n">
+        <v>0.2232411056756973</v>
+      </c>
+      <c r="FV10" t="n">
+        <v>0.0131131187081337</v>
+      </c>
+      <c r="FW10" t="n">
+        <v>0.08733583241701126</v>
+      </c>
+      <c r="FX10" t="n">
+        <v>0.03315214067697525</v>
+      </c>
+      <c r="FY10" t="n">
+        <v>0.1115889698266983</v>
+      </c>
+      <c r="FZ10" t="n">
+        <v>0.2015421092510223</v>
+      </c>
+      <c r="GA10" t="n">
+        <v>0.04815369471907616</v>
+      </c>
+      <c r="GB10" t="n">
+        <v>0.008281196467578411</v>
+      </c>
+      <c r="GC10" t="n">
+        <v>0.03076517581939697</v>
+      </c>
+      <c r="GD10" t="n">
+        <v>0.1094331443309784</v>
+      </c>
+      <c r="GE10" t="n">
+        <v>0.01990868523716927</v>
+      </c>
+      <c r="GF10" t="n">
+        <v>0.06392335891723633</v>
+      </c>
+      <c r="GG10" t="n">
+        <v>0.1203552559018135</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>6.862593826539864e-10</v>
+      </c>
+      <c r="B11" t="n">
+        <v>1.453437231679899e-10</v>
+      </c>
+      <c r="C11" t="n">
+        <v>7.248069366916354e-10</v>
+      </c>
+      <c r="D11" t="n">
+        <v>7.472495955340719e-10</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1.191173826242675e-10</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1.065511789910545e-09</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2.62740801337813e-10</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.654395279966248e-11</v>
+      </c>
+      <c r="I11" t="n">
+        <v>5.049204387930217e-10</v>
+      </c>
+      <c r="J11" t="n">
+        <v>4.413776566458694e-10</v>
+      </c>
+      <c r="K11" t="n">
+        <v>5.546402226386249e-10</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.060370236061203e-09</v>
+      </c>
+      <c r="M11" t="n">
+        <v>5.710008507686659e-11</v>
+      </c>
+      <c r="N11" t="n">
+        <v>7.467257923110537e-10</v>
+      </c>
+      <c r="O11" t="n">
+        <v>8.340095836167905e-10</v>
+      </c>
+      <c r="P11" t="n">
+        <v>7.647328326143565e-10</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>6.918099426655999e-11</v>
+      </c>
+      <c r="R11" t="n">
+        <v>8.969626708044132e-10</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.598558590527489e-10</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.94604340922433e-10</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.195688548172313e-10</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.116704576031857e-10</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.233997071192761e-10</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.353617357091608e-10</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>8.214753877133774e-11</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>8.780903781868687e-11</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>2.16639678418673e-10</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>6.365096227867184e-10</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>5.716958573209752e-10</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>8.568326048674635e-10</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>7.022196713002415e-11</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>4.162990507872166e-10</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>4.571336087444422e-10</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>3.164252193599282e-10</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>6.369826194285721e-11</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>6.69433675160036e-11</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>5.021023041784645e-10</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>1.791039538900918e-10</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>7.928564749182243e-11</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>5.885015391671189e-11</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>5.779010048279076e-10</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>3.01201341645907e-10</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>6.469270952269568e-11</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>1.172143979100149e-11</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>2.650331620834834e-10</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>5.791614410277646e-10</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>1.510405467364251e-09</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>1.914959857352017e-11</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>3.704404560878061e-10</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>6.949656405907945e-10</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>8.258305705943769e-10</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>2.577447422158485e-10</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>1.450423947613189e-10</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>2.048391734010835e-10</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>7.448804767440365e-11</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>1.403550942136178e-09</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>2.583498137642692e-10</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>9.591295535571476e-10</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>4.163902000975384e-10</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>9.801779388141085e-10</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>3.648688018387247e-10</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>1.233633473152196e-10</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>1.850921915735881e-10</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>4.632949579530532e-11</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>3.390902558741971e-10</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>2.241419272408507e-10</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>1.205156530126317e-10</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>5.203628500316526e-11</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>2.493718287421842e-10</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>3.801513270840218e-10</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>1.163845964047283e-10</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>1.68889638385572e-10</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>3.124762393280633e-10</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>5.333868902113181e-10</v>
+      </c>
+      <c r="BW11" t="n">
+        <v>3.145800286930012e-10</v>
+      </c>
+      <c r="BX11" t="n">
+        <v>2.984157088103956e-10</v>
+      </c>
+      <c r="BY11" t="n">
+        <v>7.900207155131511e-10</v>
+      </c>
+      <c r="BZ11" t="n">
+        <v>2.648593011578271e-10</v>
+      </c>
+      <c r="CA11" t="n">
+        <v>2.700199230876166e-10</v>
+      </c>
+      <c r="CB11" t="n">
+        <v>2.819708355694672e-10</v>
+      </c>
+      <c r="CC11" t="n">
+        <v>4.058812175244952e-10</v>
+      </c>
+      <c r="CD11" t="n">
+        <v>8.843131782398927e-11</v>
+      </c>
+      <c r="CE11" t="n">
+        <v>2.833585033279462e-10</v>
+      </c>
+      <c r="CF11" t="n">
+        <v>1.198333515750605e-10</v>
+      </c>
+      <c r="CG11" t="n">
+        <v>1.009645561600436e-10</v>
+      </c>
+      <c r="CH11" t="n">
+        <v>2.451023828342613e-10</v>
+      </c>
+      <c r="CI11" t="n">
+        <v>2.215139877081995e-10</v>
+      </c>
+      <c r="CJ11" t="n">
+        <v>1.742231220402957e-10</v>
+      </c>
+      <c r="CK11" t="n">
+        <v>6.209461764217217e-12</v>
+      </c>
+      <c r="CL11" t="n">
+        <v>6.96762699620157e-12</v>
+      </c>
+      <c r="CM11" t="n">
+        <v>2.255095277181596e-10</v>
+      </c>
+      <c r="CN11" t="n">
+        <v>1.01192929036209e-10</v>
+      </c>
+      <c r="CO11" t="n">
+        <v>5.650399592660449e-11</v>
+      </c>
+      <c r="CP11" t="n">
+        <v>2.335342197401502e-10</v>
+      </c>
+      <c r="CQ11" t="n">
+        <v>1.541107019775723e-09</v>
+      </c>
+      <c r="CR11" t="n">
+        <v>3.404220794145374e-10</v>
+      </c>
+      <c r="CS11" t="n">
+        <v>2.207019844657765e-10</v>
+      </c>
+      <c r="CT11" t="n">
+        <v>3.659650638088152e-10</v>
+      </c>
+      <c r="CU11" t="n">
+        <v>1.053070269874112e-10</v>
+      </c>
+      <c r="CV11" t="n">
+        <v>3.082642474616648e-11</v>
+      </c>
+      <c r="CW11" t="n">
+        <v>1.389635073678619e-10</v>
+      </c>
+      <c r="CX11" t="n">
+        <v>1.880081923477661e-10</v>
+      </c>
+      <c r="CY11" t="n">
+        <v>2.105160837317932e-11</v>
+      </c>
+      <c r="CZ11" t="n">
+        <v>2.024843070991267e-10</v>
+      </c>
+      <c r="DA11" t="n">
+        <v>2.337585403022757e-10</v>
+      </c>
+      <c r="DB11" t="n">
+        <v>1.198744992159106e-10</v>
+      </c>
+      <c r="DC11" t="n">
+        <v>6.08922912093135e-11</v>
+      </c>
+      <c r="DD11" t="n">
+        <v>1.297589674598143e-10</v>
+      </c>
+      <c r="DE11" t="n">
+        <v>4.538550091304216e-10</v>
+      </c>
+      <c r="DF11" t="n">
+        <v>7.25214666097429e-10</v>
+      </c>
+      <c r="DG11" t="n">
+        <v>3.970653528195811e-10</v>
+      </c>
+      <c r="DH11" t="n">
+        <v>2.042626484621834e-10</v>
+      </c>
+      <c r="DI11" t="n">
+        <v>4.533556308139453e-10</v>
+      </c>
+      <c r="DJ11" t="n">
+        <v>4.794374897088005e-10</v>
+      </c>
+      <c r="DK11" t="n">
+        <v>4.51651993582658e-10</v>
+      </c>
+      <c r="DL11" t="n">
+        <v>6.206398173169703e-10</v>
+      </c>
+      <c r="DM11" t="n">
+        <v>8.645107962834686e-10</v>
+      </c>
+      <c r="DN11" t="n">
+        <v>4.210575221819113e-10</v>
+      </c>
+      <c r="DO11" t="n">
+        <v>4.226923255856718e-10</v>
+      </c>
+      <c r="DP11" t="n">
+        <v>1.407200606040604e-10</v>
+      </c>
+      <c r="DQ11" t="n">
+        <v>5.534432911957765e-10</v>
+      </c>
+      <c r="DR11" t="n">
+        <v>1.002474214750748e-10</v>
+      </c>
+      <c r="DS11" t="n">
+        <v>5.473906883324275e-10</v>
+      </c>
+      <c r="DT11" t="n">
+        <v>2.159170064963689e-11</v>
+      </c>
+      <c r="DU11" t="n">
+        <v>1.652067788127098e-10</v>
+      </c>
+      <c r="DV11" t="n">
+        <v>2.161313628068484e-10</v>
+      </c>
+      <c r="DW11" t="n">
+        <v>1.511899772044245e-10</v>
+      </c>
+      <c r="DX11" t="n">
+        <v>8.651963173678112e-11</v>
+      </c>
+      <c r="DY11" t="n">
+        <v>1.278759736988988e-10</v>
+      </c>
+      <c r="DZ11" t="n">
+        <v>6.10374195630925e-10</v>
+      </c>
+      <c r="EA11" t="n">
+        <v>1.222458356764378e-09</v>
+      </c>
+      <c r="EB11" t="n">
+        <v>6.121547713178188e-10</v>
+      </c>
+      <c r="EC11" t="n">
+        <v>1.028450241635781e-10</v>
+      </c>
+      <c r="ED11" t="n">
+        <v>5.729942562093804e-12</v>
+      </c>
+      <c r="EE11" t="n">
+        <v>8.71734906482402e-11</v>
+      </c>
+      <c r="EF11" t="n">
+        <v>2.047098185409268e-10</v>
+      </c>
+      <c r="EG11" t="n">
+        <v>6.079168279882197e-10</v>
+      </c>
+      <c r="EH11" t="n">
+        <v>1.832134027823784e-10</v>
+      </c>
+      <c r="EI11" t="n">
+        <v>3.446990470834521e-10</v>
+      </c>
+      <c r="EJ11" t="n">
+        <v>2.459725756409625e-10</v>
+      </c>
+      <c r="EK11" t="n">
+        <v>2.57859955610229e-10</v>
+      </c>
+      <c r="EL11" t="n">
+        <v>1.472130056745513e-10</v>
+      </c>
+      <c r="EM11" t="n">
+        <v>3.505517265356417e-10</v>
+      </c>
+      <c r="EN11" t="n">
+        <v>1.2613879385448e-10</v>
+      </c>
+      <c r="EO11" t="n">
+        <v>2.058137549276751e-10</v>
+      </c>
+      <c r="EP11" t="n">
+        <v>2.554894906747762e-10</v>
+      </c>
+      <c r="EQ11" t="n">
+        <v>2.778571261963236e-10</v>
+      </c>
+      <c r="ER11" t="n">
+        <v>4.581384577262426e-11</v>
+      </c>
+      <c r="ES11" t="n">
+        <v>6.483297232406926e-11</v>
+      </c>
+      <c r="ET11" t="n">
+        <v>3.474844856299342e-10</v>
+      </c>
+      <c r="EU11" t="n">
+        <v>2.876894833470089e-10</v>
+      </c>
+      <c r="EV11" t="n">
+        <v>1.69136385452795e-10</v>
+      </c>
+      <c r="EW11" t="n">
+        <v>1.87552265384916e-10</v>
+      </c>
+      <c r="EX11" t="n">
+        <v>1.328651494381106e-10</v>
+      </c>
+      <c r="EY11" t="n">
+        <v>1.934520182933497e-10</v>
+      </c>
+      <c r="EZ11" t="n">
+        <v>1.588799924956419e-10</v>
+      </c>
+      <c r="FA11" t="n">
+        <v>6.309511246804789e-11</v>
+      </c>
+      <c r="FB11" t="n">
+        <v>2.118030612008326e-10</v>
+      </c>
+      <c r="FC11" t="n">
+        <v>2.425017964213794e-10</v>
+      </c>
+      <c r="FD11" t="n">
+        <v>1.304627794684876e-10</v>
+      </c>
+      <c r="FE11" t="n">
+        <v>8.193487555097079e-11</v>
+      </c>
+      <c r="FF11" t="n">
+        <v>2.671667748144202e-11</v>
+      </c>
+      <c r="FG11" t="n">
+        <v>1.026308343865523e-10</v>
+      </c>
+      <c r="FH11" t="n">
+        <v>4.775851936145159e-11</v>
+      </c>
+      <c r="FI11" t="n">
+        <v>6.197993229761778e-10</v>
+      </c>
+      <c r="FJ11" t="n">
+        <v>7.296471760120937e-10</v>
+      </c>
+      <c r="FK11" t="n">
+        <v>5.653501278235495e-11</v>
+      </c>
+      <c r="FL11" t="n">
+        <v>1.480976313805726e-10</v>
+      </c>
+      <c r="FM11" t="n">
+        <v>3.422234370886734e-11</v>
+      </c>
+      <c r="FN11" t="n">
+        <v>3.769143608334247e-10</v>
+      </c>
+      <c r="FO11" t="n">
+        <v>2.24975787999071e-10</v>
+      </c>
+      <c r="FP11" t="n">
+        <v>1.416513573104794e-09</v>
+      </c>
+      <c r="FQ11" t="n">
+        <v>1.15722667559659e-10</v>
+      </c>
+      <c r="FR11" t="n">
+        <v>9.793285071779678e-10</v>
+      </c>
+      <c r="FS11" t="n">
+        <v>1.412876260431517e-09</v>
+      </c>
+      <c r="FT11" t="n">
+        <v>4.604167880284393e-10</v>
+      </c>
+      <c r="FU11" t="n">
+        <v>2.006177723945513e-10</v>
+      </c>
+      <c r="FV11" t="n">
+        <v>1.105310565296946e-10</v>
+      </c>
+      <c r="FW11" t="n">
+        <v>2.841615831528088e-10</v>
+      </c>
+      <c r="FX11" t="n">
+        <v>9.73624236788595e-11</v>
+      </c>
+      <c r="FY11" t="n">
+        <v>1.024665630122712e-10</v>
+      </c>
+      <c r="FZ11" t="n">
+        <v>3.238095624968906e-10</v>
+      </c>
+      <c r="GA11" t="n">
+        <v>2.691322720238531e-10</v>
+      </c>
+      <c r="GB11" t="n">
+        <v>5.561757998595596e-11</v>
+      </c>
+      <c r="GC11" t="n">
+        <v>3.619520239084295e-10</v>
+      </c>
+      <c r="GD11" t="n">
+        <v>5.404222069849141e-10</v>
+      </c>
+      <c r="GE11" t="n">
+        <v>4.505103234908603e-10</v>
+      </c>
+      <c r="GF11" t="n">
+        <v>4.765072780799073e-10</v>
+      </c>
+      <c r="GG11" t="n">
+        <v>7.601982932037288e-11</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>0.08748293668031693</v>
+      </c>
+      <c r="B12" t="n">
+        <v>0.4046180844306946</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.3199349045753479</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.03353327512741089</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.0002908613532781601</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.3967399001121521</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.1101067662239075</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.003829311579465866</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.003858241951093078</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.07607337087392807</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.3880398869514465</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.4202301204204559</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.1000013947486877</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.1536196768283844</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.2619838714599609</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0.1015416830778122</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.04913043603301048</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.03345926478505135</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.003253842703998089</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0.01951434463262558</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0.09684588015079498</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0.008019822649657726</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0.009202407673001289</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0.214382216334343</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0.02740386873483658</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0.01741889491677284</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0.09654006361961365</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.1309875845909119</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0.06703419983386993</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.08056048303842545</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0.1276635974645615</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>0.1461956351995468</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0.2162787765264511</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>0.1179964691400528</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>0.06463126093149185</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0.01336204633116722</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>0.06747206300497055</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0.176687628030777</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>0.1461690962314606</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>0.01890694536268711</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0.1488759964704514</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>0.1512150317430496</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>0.01960030570626259</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>0.02942698076367378</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>0.03847804665565491</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>0.02616858296096325</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>0.2675216794013977</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>0.1763843595981598</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>0.04437102004885674</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>0.06092806905508041</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>0.2146133035421371</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>0.02398240566253662</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>0.005686012096703053</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>0.04133274778723717</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>0.09449531137943268</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>0.01687169075012207</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>0.1630760431289673</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>0.01044571027159691</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>0.003129070857539773</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>0.04995312169194221</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>0.1421731263399124</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>0.1471889913082123</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>0.002414122223854065</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>0.03888534009456635</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>0.005233021453022957</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>0.08742933720350266</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>0.1158003285527229</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>0.006150834728032351</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>0.08703786879777908</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>0.1129564642906189</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>0.003965683281421661</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>0.04511727020144463</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>0.04803633317351341</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>0.1437258571386337</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>0.1622506827116013</v>
+      </c>
+      <c r="BX12" t="n">
+        <v>0.04643805325031281</v>
+      </c>
+      <c r="BY12" t="n">
+        <v>0.03025515004992485</v>
+      </c>
+      <c r="BZ12" t="n">
+        <v>0.2690480053424835</v>
+      </c>
+      <c r="CA12" t="n">
+        <v>0.006344886496663094</v>
+      </c>
+      <c r="CB12" t="n">
+        <v>0.05073851346969604</v>
+      </c>
+      <c r="CC12" t="n">
+        <v>0.03693393617868423</v>
+      </c>
+      <c r="CD12" t="n">
+        <v>0.02129733562469482</v>
+      </c>
+      <c r="CE12" t="n">
+        <v>0.1500692218542099</v>
+      </c>
+      <c r="CF12" t="n">
+        <v>0.09767374396324158</v>
+      </c>
+      <c r="CG12" t="n">
+        <v>3.781169652938843e-07</v>
+      </c>
+      <c r="CH12" t="n">
+        <v>0.04280650988221169</v>
+      </c>
+      <c r="CI12" t="n">
+        <v>0.06458893418312073</v>
+      </c>
+      <c r="CJ12" t="n">
+        <v>0.01170982234179974</v>
+      </c>
+      <c r="CK12" t="n">
+        <v>0.02914507314562798</v>
+      </c>
+      <c r="CL12" t="n">
+        <v>0.0286279059946537</v>
+      </c>
+      <c r="CM12" t="n">
+        <v>0.0950796976685524</v>
+      </c>
+      <c r="CN12" t="n">
+        <v>0.1446919143199921</v>
+      </c>
+      <c r="CO12" t="n">
+        <v>0.2392382323741913</v>
+      </c>
+      <c r="CP12" t="n">
+        <v>0.1683989018201828</v>
+      </c>
+      <c r="CQ12" t="n">
+        <v>0.0234309695661068</v>
+      </c>
+      <c r="CR12" t="n">
+        <v>0.04048244655132294</v>
+      </c>
+      <c r="CS12" t="n">
+        <v>0.02335119992494583</v>
+      </c>
+      <c r="CT12" t="n">
+        <v>0.04385673254728317</v>
+      </c>
+      <c r="CU12" t="n">
+        <v>0.05016117542982101</v>
+      </c>
+      <c r="CV12" t="n">
+        <v>0.02168348804116249</v>
+      </c>
+      <c r="CW12" t="n">
+        <v>0.1496986150741577</v>
+      </c>
+      <c r="CX12" t="n">
+        <v>0.1047650203108788</v>
+      </c>
+      <c r="CY12" t="n">
+        <v>0.01947936229407787</v>
+      </c>
+      <c r="CZ12" t="n">
+        <v>0.008091392926871777</v>
+      </c>
+      <c r="DA12" t="n">
+        <v>0.0754796490073204</v>
+      </c>
+      <c r="DB12" t="n">
+        <v>0.03143367916345596</v>
+      </c>
+      <c r="DC12" t="n">
+        <v>0.03794150054454803</v>
+      </c>
+      <c r="DD12" t="n">
+        <v>0.007372425869107246</v>
+      </c>
+      <c r="DE12" t="n">
+        <v>0.08937488496303558</v>
+      </c>
+      <c r="DF12" t="n">
+        <v>0.1711575835943222</v>
+      </c>
+      <c r="DG12" t="n">
+        <v>0.02124495431780815</v>
+      </c>
+      <c r="DH12" t="n">
+        <v>0.04111440107226372</v>
+      </c>
+      <c r="DI12" t="n">
+        <v>0.1385720521211624</v>
+      </c>
+      <c r="DJ12" t="n">
+        <v>0.312148779630661</v>
+      </c>
+      <c r="DK12" t="n">
+        <v>0.08034945279359818</v>
+      </c>
+      <c r="DL12" t="n">
+        <v>0.15479975938797</v>
+      </c>
+      <c r="DM12" t="n">
+        <v>0.03829913586378098</v>
+      </c>
+      <c r="DN12" t="n">
+        <v>0.02929872088134289</v>
+      </c>
+      <c r="DO12" t="n">
+        <v>0.198879599571228</v>
+      </c>
+      <c r="DP12" t="n">
+        <v>0.06190910935401917</v>
+      </c>
+      <c r="DQ12" t="n">
+        <v>0.005284468177706003</v>
+      </c>
+      <c r="DR12" t="n">
+        <v>0.02116427198052406</v>
+      </c>
+      <c r="DS12" t="n">
+        <v>0.0225550215691328</v>
+      </c>
+      <c r="DT12" t="n">
+        <v>0.01971571147441864</v>
+      </c>
+      <c r="DU12" t="n">
+        <v>0.01001476403325796</v>
+      </c>
+      <c r="DV12" t="n">
+        <v>0.09485415369272232</v>
+      </c>
+      <c r="DW12" t="n">
+        <v>0.01643316075205803</v>
+      </c>
+      <c r="DX12" t="n">
+        <v>0.02569715864956379</v>
+      </c>
+      <c r="DY12" t="n">
+        <v>0.1701036393642426</v>
+      </c>
+      <c r="DZ12" t="n">
+        <v>0.01304416730999947</v>
+      </c>
+      <c r="EA12" t="n">
+        <v>0.06874944269657135</v>
+      </c>
+      <c r="EB12" t="n">
+        <v>0.09457218647003174</v>
+      </c>
+      <c r="EC12" t="n">
+        <v>0.02357986569404602</v>
+      </c>
+      <c r="ED12" t="n">
+        <v>0.1113120391964912</v>
+      </c>
+      <c r="EE12" t="n">
+        <v>0.1422030627727509</v>
+      </c>
+      <c r="EF12" t="n">
+        <v>0.009617743082344532</v>
+      </c>
+      <c r="EG12" t="n">
+        <v>0.1396831423044205</v>
+      </c>
+      <c r="EH12" t="n">
+        <v>0.03978182375431061</v>
+      </c>
+      <c r="EI12" t="n">
+        <v>0.03983596339821815</v>
+      </c>
+      <c r="EJ12" t="n">
+        <v>0.05949421226978302</v>
+      </c>
+      <c r="EK12" t="n">
+        <v>0.01099290605634451</v>
+      </c>
+      <c r="EL12" t="n">
+        <v>0.006201544776558876</v>
+      </c>
+      <c r="EM12" t="n">
+        <v>0.008809641934931278</v>
+      </c>
+      <c r="EN12" t="n">
+        <v>0.005750179756432772</v>
+      </c>
+      <c r="EO12" t="n">
+        <v>0.007028381340205669</v>
+      </c>
+      <c r="EP12" t="n">
+        <v>0.094682976603508</v>
+      </c>
+      <c r="EQ12" t="n">
+        <v>0.1054796576499939</v>
+      </c>
+      <c r="ER12" t="n">
+        <v>0.05070704966783524</v>
+      </c>
+      <c r="ES12" t="n">
+        <v>0.04683711752295494</v>
+      </c>
+      <c r="ET12" t="n">
+        <v>0.02577177062630653</v>
+      </c>
+      <c r="EU12" t="n">
+        <v>0.02999710291624069</v>
+      </c>
+      <c r="EV12" t="n">
+        <v>0.01656230166554451</v>
+      </c>
+      <c r="EW12" t="n">
+        <v>0.09594885259866714</v>
+      </c>
+      <c r="EX12" t="n">
+        <v>0.01490703411400318</v>
+      </c>
+      <c r="EY12" t="n">
+        <v>0.1837208867073059</v>
+      </c>
+      <c r="EZ12" t="n">
+        <v>0.07873141765594482</v>
+      </c>
+      <c r="FA12" t="n">
+        <v>0.01153365150094032</v>
+      </c>
+      <c r="FB12" t="n">
+        <v>0.03252081945538521</v>
+      </c>
+      <c r="FC12" t="n">
+        <v>0.07983474433422089</v>
+      </c>
+      <c r="FD12" t="n">
+        <v>0.01927474699914455</v>
+      </c>
+      <c r="FE12" t="n">
+        <v>0.04215718060731888</v>
+      </c>
+      <c r="FF12" t="n">
+        <v>0.001015986781567335</v>
+      </c>
+      <c r="FG12" t="n">
+        <v>0.01949026249349117</v>
+      </c>
+      <c r="FH12" t="n">
+        <v>0.02715481258928776</v>
+      </c>
+      <c r="FI12" t="n">
+        <v>0.06537128239870071</v>
+      </c>
+      <c r="FJ12" t="n">
+        <v>0.04372469335794449</v>
+      </c>
+      <c r="FK12" t="n">
+        <v>0.04061888158321381</v>
+      </c>
+      <c r="FL12" t="n">
+        <v>0.1256015747785568</v>
+      </c>
+      <c r="FM12" t="n">
+        <v>0.008935390040278435</v>
+      </c>
+      <c r="FN12" t="n">
+        <v>0.02677277661859989</v>
+      </c>
+      <c r="FO12" t="n">
+        <v>0.1150712519884109</v>
+      </c>
+      <c r="FP12" t="n">
+        <v>0.1084100902080536</v>
+      </c>
+      <c r="FQ12" t="n">
+        <v>0.1691184043884277</v>
+      </c>
+      <c r="FR12" t="n">
+        <v>0.006024584174156189</v>
+      </c>
+      <c r="FS12" t="n">
+        <v>0.07717897742986679</v>
+      </c>
+      <c r="FT12" t="n">
+        <v>0.06029925122857094</v>
+      </c>
+      <c r="FU12" t="n">
+        <v>0.2077625393867493</v>
+      </c>
+      <c r="FV12" t="n">
+        <v>0.01399565022438765</v>
+      </c>
+      <c r="FW12" t="n">
+        <v>0.03350687026977539</v>
+      </c>
+      <c r="FX12" t="n">
+        <v>0.1324989646673203</v>
+      </c>
+      <c r="FY12" t="n">
+        <v>0.06233595311641693</v>
+      </c>
+      <c r="FZ12" t="n">
+        <v>0.1657755225896835</v>
+      </c>
+      <c r="GA12" t="n">
+        <v>0.1422468572854996</v>
+      </c>
+      <c r="GB12" t="n">
+        <v>0.01383145712316036</v>
+      </c>
+      <c r="GC12" t="n">
+        <v>0.1056112051010132</v>
+      </c>
+      <c r="GD12" t="n">
+        <v>0.1425203233957291</v>
+      </c>
+      <c r="GE12" t="n">
+        <v>0.09515610337257385</v>
+      </c>
+      <c r="GF12" t="n">
+        <v>0.01881694421172142</v>
+      </c>
+      <c r="GG12" t="n">
+        <v>0.01304515730589628</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>1.548980981169734e-05</v>
+      </c>
+      <c r="B13" t="n">
+        <v>0.000146858423249796</v>
+      </c>
+      <c r="C13" t="n">
+        <v>6.531423423439264e-05</v>
+      </c>
+      <c r="D13" t="n">
+        <v>3.386711978237145e-05</v>
+      </c>
+      <c r="E13" t="n">
+        <v>5.715860970667563e-05</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.0001853818248491734</v>
+      </c>
+      <c r="G13" t="n">
+        <v>5.302825957187451e-05</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.0001039357593981549</v>
+      </c>
+      <c r="I13" t="n">
+        <v>3.478995495242998e-05</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3.29170361510478e-05</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.0001786226785043254</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.0001088504359358922</v>
+      </c>
+      <c r="M13" t="n">
+        <v>7.921393262222409e-05</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.000165566525538452</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.0002249643730465323</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.264613794977777e-05</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>5.051994594396092e-05</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.963704744412098e-05</v>
+      </c>
+      <c r="S13" t="n">
+        <v>8.105152119242121e-06</v>
+      </c>
+      <c r="T13" t="n">
+        <v>8.627162060292903e-06</v>
+      </c>
+      <c r="U13" t="n">
+        <v>3.188980190316215e-05</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.25309652503347e-05</v>
+      </c>
+      <c r="W13" t="n">
+        <v>2.204055090260226e-05</v>
+      </c>
+      <c r="X13" t="n">
+        <v>4.95764943480026e-05</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>3.702294634422287e-05</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>5.746751048718579e-05</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.910633909574244e-05</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>4.93006082251668e-05</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>7.820612154318951e-06</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>4.883965630142484e-06</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>4.95236054121051e-05</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>4.162234108662233e-05</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>7.043359073577449e-05</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>5.013430836697808e-06</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>9.999524627346545e-05</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.269798030989477e-05</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>2.279764703416731e-05</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>1.796341166482307e-05</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>3.330646904942114e-06</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>2.179624789278023e-05</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>3.066610952373594e-05</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>3.313510205771308e-06</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>1.068528126779711e-05</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>4.63645628769882e-05</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>4.665928372560302e-06</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>1.714187601464801e-05</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>0.0001726893824525177</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>4.1953258914873e-05</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>3.624037344707176e-05</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>8.807077392702922e-05</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>0.0001326360070379451</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>1.00410125014605e-06</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>1.924907155625988e-05</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>8.427905413554981e-06</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>1.395150684402324e-05</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>9.330437023891136e-06</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>2.193967156927101e-05</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>4.542242822935805e-05</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>3.737858060048893e-05</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>6.085869244998321e-06</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>2.564712667663116e-05</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>0.0001120902088587172</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>5.028574378229678e-05</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>4.165295649727341e-06</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>5.031042019254528e-05</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>3.675997140817344e-05</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>1.520228215667885e-05</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>2.962432881759014e-05</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>3.011148146470077e-05</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>6.754031346645206e-05</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>3.180418843840016e-06</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>4.227420868119225e-05</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>1.480030368838925e-05</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>8.083133434411138e-05</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>1.868515573733021e-05</v>
+      </c>
+      <c r="BX13" t="n">
+        <v>3.011012086062692e-05</v>
+      </c>
+      <c r="BY13" t="n">
+        <v>2.406494968454354e-05</v>
+      </c>
+      <c r="BZ13" t="n">
+        <v>7.967611600179225e-05</v>
+      </c>
+      <c r="CA13" t="n">
+        <v>2.585567199275829e-05</v>
+      </c>
+      <c r="CB13" t="n">
+        <v>1.890782004920766e-05</v>
+      </c>
+      <c r="CC13" t="n">
+        <v>8.690856702742167e-06</v>
+      </c>
+      <c r="CD13" t="n">
+        <v>3.217697212676285e-06</v>
+      </c>
+      <c r="CE13" t="n">
+        <v>4.36405316577293e-05</v>
+      </c>
+      <c r="CF13" t="n">
+        <v>1.44699142765603e-05</v>
+      </c>
+      <c r="CG13" t="n">
+        <v>1.996898208744824e-05</v>
+      </c>
+      <c r="CH13" t="n">
+        <v>2.593517092464026e-05</v>
+      </c>
+      <c r="CI13" t="n">
+        <v>4.578910738928244e-05</v>
+      </c>
+      <c r="CJ13" t="n">
+        <v>9.817690624913666e-06</v>
+      </c>
+      <c r="CK13" t="n">
+        <v>1.985973176488187e-05</v>
+      </c>
+      <c r="CL13" t="n">
+        <v>1.63289387273835e-05</v>
+      </c>
+      <c r="CM13" t="n">
+        <v>2.046187546511646e-06</v>
+      </c>
+      <c r="CN13" t="n">
+        <v>5.687492375727743e-05</v>
+      </c>
+      <c r="CO13" t="n">
+        <v>2.476402187312488e-05</v>
+      </c>
+      <c r="CP13" t="n">
+        <v>0.0001073316961992532</v>
+      </c>
+      <c r="CQ13" t="n">
+        <v>7.043606274237391e-06</v>
+      </c>
+      <c r="CR13" t="n">
+        <v>2.330489951418713e-05</v>
+      </c>
+      <c r="CS13" t="n">
+        <v>1.123128822655417e-05</v>
+      </c>
+      <c r="CT13" t="n">
+        <v>6.514571578009054e-05</v>
+      </c>
+      <c r="CU13" t="n">
+        <v>1.077639080904191e-05</v>
+      </c>
+      <c r="CV13" t="n">
+        <v>1.292190609092358e-05</v>
+      </c>
+      <c r="CW13" t="n">
+        <v>3.64702646038495e-05</v>
+      </c>
+      <c r="CX13" t="n">
+        <v>1.78614427568391e-05</v>
+      </c>
+      <c r="CY13" t="n">
+        <v>2.951055466837715e-05</v>
+      </c>
+      <c r="CZ13" t="n">
+        <v>2.438846604491118e-05</v>
+      </c>
+      <c r="DA13" t="n">
+        <v>5.672605766449124e-05</v>
+      </c>
+      <c r="DB13" t="n">
+        <v>2.459021743561607e-06</v>
+      </c>
+      <c r="DC13" t="n">
+        <v>1.743846223689616e-05</v>
+      </c>
+      <c r="DD13" t="n">
+        <v>1.405463990522549e-05</v>
+      </c>
+      <c r="DE13" t="n">
+        <v>1.403267833666177e-05</v>
+      </c>
+      <c r="DF13" t="n">
+        <v>6.88230647938326e-05</v>
+      </c>
+      <c r="DG13" t="n">
+        <v>1.627264282433316e-05</v>
+      </c>
+      <c r="DH13" t="n">
+        <v>3.163372184644686e-06</v>
+      </c>
+      <c r="DI13" t="n">
+        <v>7.129069854272529e-05</v>
+      </c>
+      <c r="DJ13" t="n">
+        <v>9.806824527913705e-05</v>
+      </c>
+      <c r="DK13" t="n">
+        <v>3.292578912805766e-05</v>
+      </c>
+      <c r="DL13" t="n">
+        <v>3.330928393552313e-06</v>
+      </c>
+      <c r="DM13" t="n">
+        <v>6.093090178183047e-06</v>
+      </c>
+      <c r="DN13" t="n">
+        <v>2.562379904702539e-06</v>
+      </c>
+      <c r="DO13" t="n">
+        <v>9.710610356705729e-06</v>
+      </c>
+      <c r="DP13" t="n">
+        <v>9.889191460388247e-06</v>
+      </c>
+      <c r="DQ13" t="n">
+        <v>2.011254218814429e-05</v>
+      </c>
+      <c r="DR13" t="n">
+        <v>2.393345675955061e-05</v>
+      </c>
+      <c r="DS13" t="n">
+        <v>2.001363463932648e-05</v>
+      </c>
+      <c r="DT13" t="n">
+        <v>2.671987567737233e-05</v>
+      </c>
+      <c r="DU13" t="n">
+        <v>3.381674468982965e-05</v>
+      </c>
+      <c r="DV13" t="n">
+        <v>7.278396878973581e-06</v>
+      </c>
+      <c r="DW13" t="n">
+        <v>1.776743010850623e-05</v>
+      </c>
+      <c r="DX13" t="n">
+        <v>4.615173111233162e-06</v>
+      </c>
+      <c r="DY13" t="n">
+        <v>4.351932147983462e-05</v>
+      </c>
+      <c r="DZ13" t="n">
+        <v>3.32121599058155e-05</v>
+      </c>
+      <c r="EA13" t="n">
+        <v>2.216500433860347e-05</v>
+      </c>
+      <c r="EB13" t="n">
+        <v>1.122523599406122e-06</v>
+      </c>
+      <c r="EC13" t="n">
+        <v>5.924376637267414e-06</v>
+      </c>
+      <c r="ED13" t="n">
+        <v>6.778365059290081e-05</v>
+      </c>
+      <c r="EE13" t="n">
+        <v>7.977441418915987e-05</v>
+      </c>
+      <c r="EF13" t="n">
+        <v>2.826289801305393e-06</v>
+      </c>
+      <c r="EG13" t="n">
+        <v>3.134147118544206e-05</v>
+      </c>
+      <c r="EH13" t="n">
+        <v>1.332502506556921e-05</v>
+      </c>
+      <c r="EI13" t="n">
+        <v>1.982744470296893e-05</v>
+      </c>
+      <c r="EJ13" t="n">
+        <v>1.963637805602048e-05</v>
+      </c>
+      <c r="EK13" t="n">
+        <v>4.312366218073294e-05</v>
+      </c>
+      <c r="EL13" t="n">
+        <v>1.333561431238195e-05</v>
+      </c>
+      <c r="EM13" t="n">
+        <v>4.899853593087755e-06</v>
+      </c>
+      <c r="EN13" t="n">
+        <v>6.217756890691817e-06</v>
+      </c>
+      <c r="EO13" t="n">
+        <v>3.308580926386639e-05</v>
+      </c>
+      <c r="EP13" t="n">
+        <v>4.649035690817982e-05</v>
+      </c>
+      <c r="EQ13" t="n">
+        <v>3.066335193580016e-05</v>
+      </c>
+      <c r="ER13" t="n">
+        <v>1.806468753784429e-05</v>
+      </c>
+      <c r="ES13" t="n">
+        <v>1.414339749317151e-05</v>
+      </c>
+      <c r="ET13" t="n">
+        <v>4.474262095754966e-05</v>
+      </c>
+      <c r="EU13" t="n">
+        <v>1.8333654224989e-05</v>
+      </c>
+      <c r="EV13" t="n">
+        <v>1.272390181839e-05</v>
+      </c>
+      <c r="EW13" t="n">
+        <v>2.484007382008713e-05</v>
+      </c>
+      <c r="EX13" t="n">
+        <v>1.498227629781468e-05</v>
+      </c>
+      <c r="EY13" t="n">
+        <v>5.14723542437423e-05</v>
+      </c>
+      <c r="EZ13" t="n">
+        <v>1.29785994431586e-05</v>
+      </c>
+      <c r="FA13" t="n">
+        <v>3.371672937646508e-05</v>
+      </c>
+      <c r="FB13" t="n">
+        <v>1.561720273457468e-05</v>
+      </c>
+      <c r="FC13" t="n">
+        <v>4.66078708996065e-05</v>
+      </c>
+      <c r="FD13" t="n">
+        <v>8.62248725752579e-06</v>
+      </c>
+      <c r="FE13" t="n">
+        <v>9.926525308401324e-06</v>
+      </c>
+      <c r="FF13" t="n">
+        <v>5.291910383675713e-06</v>
+      </c>
+      <c r="FG13" t="n">
+        <v>6.860575012979098e-06</v>
+      </c>
+      <c r="FH13" t="n">
+        <v>4.645590888685547e-05</v>
+      </c>
+      <c r="FI13" t="n">
+        <v>1.798453922674526e-05</v>
+      </c>
+      <c r="FJ13" t="n">
+        <v>2.842177855200134e-05</v>
+      </c>
+      <c r="FK13" t="n">
+        <v>1.584395431564189e-05</v>
+      </c>
+      <c r="FL13" t="n">
+        <v>5.156793486094102e-05</v>
+      </c>
+      <c r="FM13" t="n">
+        <v>2.935633892775513e-05</v>
+      </c>
+      <c r="FN13" t="n">
+        <v>6.518689588119742e-06</v>
+      </c>
+      <c r="FO13" t="n">
+        <v>8.77572238096036e-05</v>
+      </c>
+      <c r="FP13" t="n">
+        <v>1.837262061599176e-06</v>
+      </c>
+      <c r="FQ13" t="n">
+        <v>5.719909313484095e-05</v>
+      </c>
+      <c r="FR13" t="n">
+        <v>4.275245009921491e-05</v>
+      </c>
+      <c r="FS13" t="n">
+        <v>2.263027272420004e-05</v>
+      </c>
+      <c r="FT13" t="n">
+        <v>4.765233461512253e-05</v>
+      </c>
+      <c r="FU13" t="n">
+        <v>1.725351830828004e-05</v>
+      </c>
+      <c r="FV13" t="n">
+        <v>1.091885678761173e-06</v>
+      </c>
+      <c r="FW13" t="n">
+        <v>0.0001054999811458401</v>
+      </c>
+      <c r="FX13" t="n">
+        <v>1.240944584424142e-05</v>
+      </c>
+      <c r="FY13" t="n">
+        <v>3.321157782920636e-05</v>
+      </c>
+      <c r="FZ13" t="n">
+        <v>2.613211108837277e-05</v>
+      </c>
+      <c r="GA13" t="n">
+        <v>5.793793025077321e-05</v>
+      </c>
+      <c r="GB13" t="n">
+        <v>1.759551923896652e-05</v>
+      </c>
+      <c r="GC13" t="n">
+        <v>7.645817822776735e-05</v>
+      </c>
+      <c r="GD13" t="n">
+        <v>6.872619997011498e-05</v>
+      </c>
+      <c r="GE13" t="n">
+        <v>2.376237353018951e-05</v>
+      </c>
+      <c r="GF13" t="n">
+        <v>5.767899892816786e-06</v>
+      </c>
+      <c r="GG13" t="n">
+        <v>2.94648216367932e-05</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>0.011150773614645</v>
+      </c>
+      <c r="B14" t="n">
+        <v>0.03734464198350906</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.0153839411213994</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.08279962837696075</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.03146306425333023</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.08530022203922272</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.04794186353683472</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.04553404077887535</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.01582001149654388</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.004101260099560022</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.0127182099968195</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.02562159858644009</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.1276708245277405</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.07689379155635834</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.08772037178277969</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0.06206129491329193</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.03182420879602432</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.01573293469846249</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.004692908376455307</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0.002919816877692938</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0.008388529531657696</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0.009269550442695618</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0.01585933938622475</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0.02794214896857738</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0.0002528084442019463</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0.01248771604150534</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0.001605545752681792</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.001973561942577362</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0.01050054654479027</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.008403515443205833</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0.003389774821698666</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0.0003424081951379776</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0.03312347084283829</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0.01254324801266193</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0.0289789792150259</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0.01246221456676722</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0.002277680672705173</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0.02644599229097366</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>0.009623483754694462</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>0.01953700743615627</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0.004220819100737572</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>0.007827536202967167</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>0.01903295516967773</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>0.01189862098544836</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>0.003097592620179057</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>0.02105906046926975</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>0.0203019380569458</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>0.02938113920390606</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>0.02886335179209709</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>0.07447800785303116</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>0.05003032833337784</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>0.01482362300157547</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>0.01773102581501007</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>0.01121998857706785</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>0.005013798829168081</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>0.00283298990689218</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>0.01373817306011915</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>0.001231941394507885</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>0.03429669514298439</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>0.02475995384156704</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>0.007219305261969566</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>0.01818680763244629</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>0.009746520780026913</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>0.01102200709283352</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>0.02867088839411736</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>0.01084356009960175</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>0.0275135226547718</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>0.01185206789523363</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>0.01277712173759937</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>0.007086854428052902</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>0.00129291508346796</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>0.008736873976886272</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>0.0009112129919230938</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>0.01669834926724434</v>
+      </c>
+      <c r="BW14" t="n">
+        <v>0.01123947650194168</v>
+      </c>
+      <c r="BX14" t="n">
+        <v>0.0459066778421402</v>
+      </c>
+      <c r="BY14" t="n">
+        <v>0.02182292565703392</v>
+      </c>
+      <c r="BZ14" t="n">
+        <v>0.03219463303685188</v>
+      </c>
+      <c r="CA14" t="n">
+        <v>0.01649367436766624</v>
+      </c>
+      <c r="CB14" t="n">
+        <v>0.006403720006346703</v>
+      </c>
+      <c r="CC14" t="n">
+        <v>0.0009577766177244484</v>
+      </c>
+      <c r="CD14" t="n">
+        <v>0.004236293956637383</v>
+      </c>
+      <c r="CE14" t="n">
+        <v>0.009062555618584156</v>
+      </c>
+      <c r="CF14" t="n">
+        <v>0.005419258028268814</v>
+      </c>
+      <c r="CG14" t="n">
+        <v>0.0302894152700901</v>
+      </c>
+      <c r="CH14" t="n">
+        <v>0.006617631763219833</v>
+      </c>
+      <c r="CI14" t="n">
+        <v>0.014536970295012</v>
+      </c>
+      <c r="CJ14" t="n">
+        <v>0.002303835703060031</v>
+      </c>
+      <c r="CK14" t="n">
+        <v>0.01255376171320677</v>
+      </c>
+      <c r="CL14" t="n">
+        <v>0.00830348115414381</v>
+      </c>
+      <c r="CM14" t="n">
+        <v>0.00700843520462513</v>
+      </c>
+      <c r="CN14" t="n">
+        <v>0.01188940461724997</v>
+      </c>
+      <c r="CO14" t="n">
+        <v>0.03096969611942768</v>
+      </c>
+      <c r="CP14" t="n">
+        <v>0.03798273205757141</v>
+      </c>
+      <c r="CQ14" t="n">
+        <v>0.00415314082056284</v>
+      </c>
+      <c r="CR14" t="n">
+        <v>0.006301187910139561</v>
+      </c>
+      <c r="CS14" t="n">
+        <v>0.006056899204850197</v>
+      </c>
+      <c r="CT14" t="n">
+        <v>0.02226164564490318</v>
+      </c>
+      <c r="CU14" t="n">
+        <v>0.007225415669381618</v>
+      </c>
+      <c r="CV14" t="n">
+        <v>0.002476166700944304</v>
+      </c>
+      <c r="CW14" t="n">
+        <v>0.007098733447492123</v>
+      </c>
+      <c r="CX14" t="n">
+        <v>0.007865222170948982</v>
+      </c>
+      <c r="CY14" t="n">
+        <v>0.03263780847191811</v>
+      </c>
+      <c r="CZ14" t="n">
+        <v>0.01631319336593151</v>
+      </c>
+      <c r="DA14" t="n">
+        <v>0.01668857224285603</v>
+      </c>
+      <c r="DB14" t="n">
+        <v>0.0043976497836411</v>
+      </c>
+      <c r="DC14" t="n">
+        <v>0.01311451569199562</v>
+      </c>
+      <c r="DD14" t="n">
+        <v>0.01077473256736994</v>
+      </c>
+      <c r="DE14" t="n">
+        <v>0.02005085349082947</v>
+      </c>
+      <c r="DF14" t="n">
+        <v>0.02786574326455593</v>
+      </c>
+      <c r="DG14" t="n">
+        <v>0.001108443364500999</v>
+      </c>
+      <c r="DH14" t="n">
+        <v>0.02900535427033901</v>
+      </c>
+      <c r="DI14" t="n">
+        <v>0.0120944632217288</v>
+      </c>
+      <c r="DJ14" t="n">
+        <v>0.05451752617955208</v>
+      </c>
+      <c r="DK14" t="n">
+        <v>0.00316650653257966</v>
+      </c>
+      <c r="DL14" t="n">
+        <v>0.03388996422290802</v>
+      </c>
+      <c r="DM14" t="n">
+        <v>0.01456388272345066</v>
+      </c>
+      <c r="DN14" t="n">
+        <v>0.002294695004820824</v>
+      </c>
+      <c r="DO14" t="n">
+        <v>0.02381054311990738</v>
+      </c>
+      <c r="DP14" t="n">
+        <v>0.003255508840084076</v>
+      </c>
+      <c r="DQ14" t="n">
+        <v>0.001407264266163111</v>
+      </c>
+      <c r="DR14" t="n">
+        <v>0.01564087346196175</v>
+      </c>
+      <c r="DS14" t="n">
+        <v>0.004965535365045071</v>
+      </c>
+      <c r="DT14" t="n">
+        <v>0.003347748424857855</v>
+      </c>
+      <c r="DU14" t="n">
+        <v>0.02703346684575081</v>
+      </c>
+      <c r="DV14" t="n">
+        <v>0.02322338335216045</v>
+      </c>
+      <c r="DW14" t="n">
+        <v>0.00565240066498518</v>
+      </c>
+      <c r="DX14" t="n">
+        <v>0.01326821930706501</v>
+      </c>
+      <c r="DY14" t="n">
+        <v>0.04103522747755051</v>
+      </c>
+      <c r="DZ14" t="n">
+        <v>0.03014905750751495</v>
+      </c>
+      <c r="EA14" t="n">
+        <v>0.001342651201412082</v>
+      </c>
+      <c r="EB14" t="n">
+        <v>0.0166623480618</v>
+      </c>
+      <c r="EC14" t="n">
+        <v>0.008329049684107304</v>
+      </c>
+      <c r="ED14" t="n">
+        <v>0.02797399647533894</v>
+      </c>
+      <c r="EE14" t="n">
+        <v>0.01859238930046558</v>
+      </c>
+      <c r="EF14" t="n">
+        <v>0.01791160926222801</v>
+      </c>
+      <c r="EG14" t="n">
+        <v>0.002746226033195853</v>
+      </c>
+      <c r="EH14" t="n">
+        <v>0.01237441506236792</v>
+      </c>
+      <c r="EI14" t="n">
+        <v>0.02362706325948238</v>
+      </c>
+      <c r="EJ14" t="n">
+        <v>0.004856428597122431</v>
+      </c>
+      <c r="EK14" t="n">
+        <v>0.008143207058310509</v>
+      </c>
+      <c r="EL14" t="n">
+        <v>0.002086296677589417</v>
+      </c>
+      <c r="EM14" t="n">
+        <v>0.003174914978444576</v>
+      </c>
+      <c r="EN14" t="n">
+        <v>0.008916410617530346</v>
+      </c>
+      <c r="EO14" t="n">
+        <v>0.002591043710708618</v>
+      </c>
+      <c r="EP14" t="n">
+        <v>0.01278234086930752</v>
+      </c>
+      <c r="EQ14" t="n">
+        <v>0.006708997301757336</v>
+      </c>
+      <c r="ER14" t="n">
+        <v>0.02428989857435226</v>
+      </c>
+      <c r="ES14" t="n">
+        <v>0.0005020456737838686</v>
+      </c>
+      <c r="ET14" t="n">
+        <v>0.004994713701307774</v>
+      </c>
+      <c r="EU14" t="n">
+        <v>0.007178507279604673</v>
+      </c>
+      <c r="EV14" t="n">
+        <v>0.01815173216164112</v>
+      </c>
+      <c r="EW14" t="n">
+        <v>0.02474922686815262</v>
+      </c>
+      <c r="EX14" t="n">
+        <v>0.004096250981092453</v>
+      </c>
+      <c r="EY14" t="n">
+        <v>0.01079566683620214</v>
+      </c>
+      <c r="EZ14" t="n">
+        <v>0.00235256738960743</v>
+      </c>
+      <c r="FA14" t="n">
+        <v>0.03624152392148972</v>
+      </c>
+      <c r="FB14" t="n">
+        <v>0.01024815253913403</v>
+      </c>
+      <c r="FC14" t="n">
+        <v>0.01507367938756943</v>
+      </c>
+      <c r="FD14" t="n">
+        <v>0.00526847317814827</v>
+      </c>
+      <c r="FE14" t="n">
+        <v>0.01366461720317602</v>
+      </c>
+      <c r="FF14" t="n">
+        <v>0.003840803634375334</v>
+      </c>
+      <c r="FG14" t="n">
+        <v>0.008609897457063198</v>
+      </c>
+      <c r="FH14" t="n">
+        <v>0.007045961450785398</v>
+      </c>
+      <c r="FI14" t="n">
+        <v>0.02023404836654663</v>
+      </c>
+      <c r="FJ14" t="n">
+        <v>0.01733256876468658</v>
+      </c>
+      <c r="FK14" t="n">
+        <v>0.00771486246958375</v>
+      </c>
+      <c r="FL14" t="n">
+        <v>0.02485045231878757</v>
+      </c>
+      <c r="FM14" t="n">
+        <v>0.004243343602865934</v>
+      </c>
+      <c r="FN14" t="n">
+        <v>0.02224837616086006</v>
+      </c>
+      <c r="FO14" t="n">
+        <v>0.018619230017066</v>
+      </c>
+      <c r="FP14" t="n">
+        <v>0.02723856642842293</v>
+      </c>
+      <c r="FQ14" t="n">
+        <v>0.01108873169869184</v>
+      </c>
+      <c r="FR14" t="n">
+        <v>0.03690246120095253</v>
+      </c>
+      <c r="FS14" t="n">
+        <v>0.0369207039475441</v>
+      </c>
+      <c r="FT14" t="n">
+        <v>0.0003217949997633696</v>
+      </c>
+      <c r="FU14" t="n">
+        <v>0.001234602648764849</v>
+      </c>
+      <c r="FV14" t="n">
+        <v>0.02994250133633614</v>
+      </c>
+      <c r="FW14" t="n">
+        <v>0.06414066255092621</v>
+      </c>
+      <c r="FX14" t="n">
+        <v>0.008109508082270622</v>
+      </c>
+      <c r="FY14" t="n">
+        <v>0.002880505984649062</v>
+      </c>
+      <c r="FZ14" t="n">
+        <v>0.01988630555570126</v>
+      </c>
+      <c r="GA14" t="n">
+        <v>0.02539044246077538</v>
+      </c>
+      <c r="GB14" t="n">
+        <v>0.02777763828635216</v>
+      </c>
+      <c r="GC14" t="n">
+        <v>0.03825024142861366</v>
+      </c>
+      <c r="GD14" t="n">
+        <v>0.03547536209225655</v>
+      </c>
+      <c r="GE14" t="n">
+        <v>0.01322658360004425</v>
+      </c>
+      <c r="GF14" t="n">
+        <v>0.0032814412843436</v>
+      </c>
+      <c r="GG14" t="n">
+        <v>0.003902358002960682</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>0.0003723284171428531</v>
+      </c>
+      <c r="B15" t="n">
+        <v>0.00397591246291995</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.000906716741155833</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.001475757453590631</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.0007057259208522737</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.007341335527598858</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.0001459703635191545</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.003042436437681317</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.0001536581112304702</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.000776506494730711</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.004333608318120241</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.001615676679648459</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.002822156762704253</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.003955510910600424</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.00883056502789259</v>
+      </c>
+      <c r="P15" t="n">
+        <v>7.284170715138316e-05</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.001587970764376223</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.0004122317477595061</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.000166045589139685</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0.0005952552892267704</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0.0009056996204890311</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0.0008655759738758206</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0.000317552883643657</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0.001697611412964761</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0.0007815251592546701</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0.001455476740375161</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0.0003440635045990348</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>4.697711847256869e-05</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>0.0004488004487939179</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.0001501971128163859</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>0.001972828293219209</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0.001754641532897949</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0.002407203894108534</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>0.0003509042435325682</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>0.003441336797550321</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>0.000582690816372633</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>0.0009617750765755773</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>0.001084107672795653</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>0.0007641721167601645</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>0.0004709481727331877</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0.000259734079008922</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>0.0006666829576715827</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>0.0005234731361269951</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>0.001674810773693025</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>0.0002417422365397215</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>0.0003200228966306895</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>0.004807586781680584</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>0.001276904717087746</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>0.000527235446497798</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>0.002790848724544048</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>0.006567709147930145</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>0.000660912599414587</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>0.0008476658258587122</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>0.0001848043466452509</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>0.0002545541210565716</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>0.0004700003773905337</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>0.001111763063818216</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>0.0004810716491192579</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>0.0008677978185005486</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>0.00152742094360292</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>0.001073147053830326</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>0.002925218781456351</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>0.0005389954894781113</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>0.000132192624732852</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>0.002456840127706528</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>0.000657775322906673</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>0.00109036557842046</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>0.00101617572363466</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>0.001015459187328815</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>0.001229938701726496</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>0.001186489593237638</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>0.00107230432331562</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>2.697756463021506e-05</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>0.002684330567717552</v>
+      </c>
+      <c r="BW15" t="n">
+        <v>0.0008854925399646163</v>
+      </c>
+      <c r="BX15" t="n">
+        <v>5.942006828263402e-05</v>
+      </c>
+      <c r="BY15" t="n">
+        <v>0.0008089356124401093</v>
+      </c>
+      <c r="BZ15" t="n">
+        <v>0.003736464306712151</v>
+      </c>
+      <c r="CA15" t="n">
+        <v>0.001370775513350964</v>
+      </c>
+      <c r="CB15" t="n">
+        <v>0.0006249501602724195</v>
+      </c>
+      <c r="CC15" t="n">
+        <v>0.0001279385323869064</v>
+      </c>
+      <c r="CD15" t="n">
+        <v>0.0002417051000520587</v>
+      </c>
+      <c r="CE15" t="n">
+        <v>0.001548669999465346</v>
+      </c>
+      <c r="CF15" t="n">
+        <v>0.0005993462400510907</v>
+      </c>
+      <c r="CG15" t="n">
+        <v>0.0004270597419235855</v>
+      </c>
+      <c r="CH15" t="n">
+        <v>0.0009273872710764408</v>
+      </c>
+      <c r="CI15" t="n">
+        <v>0.001782376668415964</v>
+      </c>
+      <c r="CJ15" t="n">
+        <v>0.0002955291129183024</v>
+      </c>
+      <c r="CK15" t="n">
+        <v>0.0001923315285239369</v>
+      </c>
+      <c r="CL15" t="n">
+        <v>0.0003267374122515321</v>
+      </c>
+      <c r="CM15" t="n">
+        <v>0.0007395041757263243</v>
+      </c>
+      <c r="CN15" t="n">
+        <v>0.003014770336449146</v>
+      </c>
+      <c r="CO15" t="n">
+        <v>0.002959910547360778</v>
+      </c>
+      <c r="CP15" t="n">
+        <v>0.001156014855951071</v>
+      </c>
+      <c r="CQ15" t="n">
+        <v>0.001072177547030151</v>
+      </c>
+      <c r="CR15" t="n">
+        <v>6.611157004954293e-05</v>
+      </c>
+      <c r="CS15" t="n">
+        <v>0.0006961447652429342</v>
+      </c>
+      <c r="CT15" t="n">
+        <v>0.001874626381322742</v>
+      </c>
+      <c r="CU15" t="n">
+        <v>0.0004139337397646159</v>
+      </c>
+      <c r="CV15" t="n">
+        <v>0.0002247390802949667</v>
+      </c>
+      <c r="CW15" t="n">
+        <v>0.001358506618998945</v>
+      </c>
+      <c r="CX15" t="n">
+        <v>0.0008117734687402844</v>
+      </c>
+      <c r="CY15" t="n">
+        <v>0.0007933967281132936</v>
+      </c>
+      <c r="CZ15" t="n">
+        <v>0.0008701242040842772</v>
+      </c>
+      <c r="DA15" t="n">
+        <v>0.002225239062681794</v>
+      </c>
+      <c r="DB15" t="n">
+        <v>7.314691902138293e-05</v>
+      </c>
+      <c r="DC15" t="n">
+        <v>0.0002099308185279369</v>
+      </c>
+      <c r="DD15" t="n">
+        <v>7.142803224269301e-05</v>
+      </c>
+      <c r="DE15" t="n">
+        <v>0.0002504700678400695</v>
+      </c>
+      <c r="DF15" t="n">
+        <v>0.002174692926928401</v>
+      </c>
+      <c r="DG15" t="n">
+        <v>0.0007822454208508134</v>
+      </c>
+      <c r="DH15" t="n">
+        <v>0.001287437393330038</v>
+      </c>
+      <c r="DI15" t="n">
+        <v>0.0006247180281206965</v>
+      </c>
+      <c r="DJ15" t="n">
+        <v>0.00159213924780488</v>
+      </c>
+      <c r="DK15" t="n">
+        <v>0.0001972039171960205</v>
+      </c>
+      <c r="DL15" t="n">
+        <v>0.001771047711372375</v>
+      </c>
+      <c r="DM15" t="n">
+        <v>0.0009487386560067534</v>
+      </c>
+      <c r="DN15" t="n">
+        <v>8.439201337751001e-06</v>
+      </c>
+      <c r="DO15" t="n">
+        <v>0.001342935487627983</v>
+      </c>
+      <c r="DP15" t="n">
+        <v>0.0002125799073837698</v>
+      </c>
+      <c r="DQ15" t="n">
+        <v>0.0006269033183343709</v>
+      </c>
+      <c r="DR15" t="n">
+        <v>0.0003022351302206516</v>
+      </c>
+      <c r="DS15" t="n">
+        <v>0.0005274437717162073</v>
+      </c>
+      <c r="DT15" t="n">
+        <v>0.0009470339282415807</v>
+      </c>
+      <c r="DU15" t="n">
+        <v>0.001814540009945631</v>
+      </c>
+      <c r="DV15" t="n">
+        <v>0.0008342406945303082</v>
+      </c>
+      <c r="DW15" t="n">
+        <v>0.0005555205862037838</v>
+      </c>
+      <c r="DX15" t="n">
+        <v>0.0005645339842885733</v>
+      </c>
+      <c r="DY15" t="n">
+        <v>0.002021931577473879</v>
+      </c>
+      <c r="DZ15" t="n">
+        <v>0.0001206936867674813</v>
+      </c>
+      <c r="EA15" t="n">
+        <v>0.0005176452687010169</v>
+      </c>
+      <c r="EB15" t="n">
+        <v>0.0009463190799579024</v>
+      </c>
+      <c r="EC15" t="n">
+        <v>0.0002997147385030985</v>
+      </c>
+      <c r="ED15" t="n">
+        <v>0.002380772493779659</v>
+      </c>
+      <c r="EE15" t="n">
+        <v>0.002313863951712847</v>
+      </c>
+      <c r="EF15" t="n">
+        <v>5.108979894430377e-05</v>
+      </c>
+      <c r="EG15" t="n">
+        <v>0.0001947265991475433</v>
+      </c>
+      <c r="EH15" t="n">
+        <v>0.0003275116032455117</v>
+      </c>
+      <c r="EI15" t="n">
+        <v>0.000485812226543203</v>
+      </c>
+      <c r="EJ15" t="n">
+        <v>0.00014200882287696</v>
+      </c>
+      <c r="EK15" t="n">
+        <v>0.001213253708556294</v>
+      </c>
+      <c r="EL15" t="n">
+        <v>0.000207625882467255</v>
+      </c>
+      <c r="EM15" t="n">
+        <v>0.0006096256547607481</v>
+      </c>
+      <c r="EN15" t="n">
+        <v>3.349536564201117e-05</v>
+      </c>
+      <c r="EO15" t="n">
+        <v>0.0004792012914549559</v>
+      </c>
+      <c r="EP15" t="n">
+        <v>0.0009681994561105967</v>
+      </c>
+      <c r="EQ15" t="n">
+        <v>0.0009934583213180304</v>
+      </c>
+      <c r="ER15" t="n">
+        <v>0.0009472481906414032</v>
+      </c>
+      <c r="ES15" t="n">
+        <v>0.0004821514012292027</v>
+      </c>
+      <c r="ET15" t="n">
+        <v>0.0004405035288073123</v>
+      </c>
+      <c r="EU15" t="n">
+        <v>0.0004341828753240407</v>
+      </c>
+      <c r="EV15" t="n">
+        <v>4.067289410158992e-05</v>
+      </c>
+      <c r="EW15" t="n">
+        <v>8.505239384248853e-05</v>
+      </c>
+      <c r="EX15" t="n">
+        <v>8.381061343243346e-05</v>
+      </c>
+      <c r="EY15" t="n">
+        <v>0.001696705119684339</v>
+      </c>
+      <c r="EZ15" t="n">
+        <v>0.000530308810994029</v>
+      </c>
+      <c r="FA15" t="n">
+        <v>0.0007496103644371033</v>
+      </c>
+      <c r="FB15" t="n">
+        <v>0.0006663478561677039</v>
+      </c>
+      <c r="FC15" t="n">
+        <v>0.002106195315718651</v>
+      </c>
+      <c r="FD15" t="n">
+        <v>0.0005122371949255466</v>
+      </c>
+      <c r="FE15" t="n">
+        <v>0.0001720198051771149</v>
+      </c>
+      <c r="FF15" t="n">
+        <v>0.0001706105831544846</v>
+      </c>
+      <c r="FG15" t="n">
+        <v>0.0002762001822702587</v>
+      </c>
+      <c r="FH15" t="n">
+        <v>0.001714921090751886</v>
+      </c>
+      <c r="FI15" t="n">
+        <v>0.001261931145563722</v>
+      </c>
+      <c r="FJ15" t="n">
+        <v>0.001085929805412889</v>
+      </c>
+      <c r="FK15" t="n">
+        <v>0.0009880606085062027</v>
+      </c>
+      <c r="FL15" t="n">
+        <v>0.00256394874304533</v>
+      </c>
+      <c r="FM15" t="n">
+        <v>0.0006474039983004332</v>
+      </c>
+      <c r="FN15" t="n">
+        <v>0.0008222936885431409</v>
+      </c>
+      <c r="FO15" t="n">
+        <v>0.002779352478682995</v>
+      </c>
+      <c r="FP15" t="n">
+        <v>0.0007546296110376716</v>
+      </c>
+      <c r="FQ15" t="n">
+        <v>0.001835322938859463</v>
+      </c>
+      <c r="FR15" t="n">
+        <v>0.0003174156881868839</v>
+      </c>
+      <c r="FS15" t="n">
+        <v>0.001286776619963348</v>
+      </c>
+      <c r="FT15" t="n">
+        <v>0.002328102709725499</v>
+      </c>
+      <c r="FU15" t="n">
+        <v>0.0004157900984864682</v>
+      </c>
+      <c r="FV15" t="n">
+        <v>0.0005071081686764956</v>
+      </c>
+      <c r="FW15" t="n">
+        <v>0.004340420011430979</v>
+      </c>
+      <c r="FX15" t="n">
+        <v>0.0005401052767410874</v>
+      </c>
+      <c r="FY15" t="n">
+        <v>0.0008751922287046909</v>
+      </c>
+      <c r="FZ15" t="n">
+        <v>0.001558816758915782</v>
+      </c>
+      <c r="GA15" t="n">
+        <v>0.002162928692996502</v>
+      </c>
+      <c r="GB15" t="n">
+        <v>0.0007535385084338486</v>
+      </c>
+      <c r="GC15" t="n">
+        <v>0.002533400431275368</v>
+      </c>
+      <c r="GD15" t="n">
+        <v>0.002349915448576212</v>
+      </c>
+      <c r="GE15" t="n">
+        <v>0.001095665502361953</v>
+      </c>
+      <c r="GF15" t="n">
+        <v>0.0006569401593878865</v>
+      </c>
+      <c r="GG15" t="n">
+        <v>0.000378882308723405</v>
       </c>
     </row>
   </sheetData>
